--- a/v4_data/runs/latest_pool/120d/result.xlsx
+++ b/v4_data/runs/latest_pool/120d/result.xlsx
@@ -592,7 +592,7 @@
         <v>234148960</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01258406767135452</v>
+        <v>0.0125840676713545</v>
       </c>
       <c r="K3" t="n">
         <v>10.76</v>
@@ -646,7 +646,7 @@
         <v>269070178</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01462989774402144</v>
+        <v>0.0146298977440214</v>
       </c>
       <c r="K4" t="n">
         <v>10.73</v>
@@ -700,7 +700,7 @@
         <v>293595302</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01649789997437596</v>
+        <v>0.0164978999743759</v>
       </c>
       <c r="K5" t="n">
         <v>10.41</v>
@@ -715,7 +715,7 @@
         <v>10.29</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9893100097181731</v>
+        <v>0.9893100097181732</v>
       </c>
       <c r="P5" t="n">
         <v>0.922298061130514</v>
@@ -754,7 +754,7 @@
         <v>212921244</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01199140461198869</v>
+        <v>0.0119914046119886</v>
       </c>
       <c r="K6" t="n">
         <v>10.29</v>
@@ -769,7 +769,7 @@
         <v>10.16</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9891732283464567</v>
+        <v>0.9891732283464568</v>
       </c>
       <c r="P6" t="n">
         <v>0.7952107938133974</v>
@@ -808,7 +808,7 @@
         <v>177464960</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01013514572971141</v>
+        <v>0.0101351457297114</v>
       </c>
       <c r="K7" t="n">
         <v>10.16</v>
@@ -862,7 +862,7 @@
         <v>290497870</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01701339246066282</v>
+        <v>0.0170133924606628</v>
       </c>
       <c r="K8" t="n">
         <v>10.02</v>
@@ -877,7 +877,7 @@
         <v>9.789999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9887640449438203</v>
+        <v>0.9887640449438204</v>
       </c>
       <c r="P8" t="n">
         <v>1.292056641373226</v>
@@ -916,7 +916,7 @@
         <v>215518490</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01276117760751107</v>
+        <v>0.012761177607511</v>
       </c>
       <c r="K9" t="n">
         <v>9.789999999999999</v>
@@ -931,10 +931,10 @@
         <v>9.76</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9887295081967213</v>
+        <v>0.9887295081967212</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9080395579064359</v>
+        <v>0.908039557906436</v>
       </c>
     </row>
     <row r="10">
@@ -970,7 +970,7 @@
         <v>292012221</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01815232946203914</v>
+        <v>0.0181523294620391</v>
       </c>
       <c r="K10" t="n">
         <v>9.550000000000001</v>
@@ -985,7 +985,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9889502762430937</v>
+        <v>0.9889502762430936</v>
       </c>
       <c r="P10" t="n">
         <v>1.326943672589427</v>
@@ -1024,7 +1024,7 @@
         <v>208293720</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01302650843374025</v>
+        <v>0.0130265084337402</v>
       </c>
       <c r="K11" t="n">
         <v>9.279999999999999</v>
@@ -1042,7 +1042,7 @@
         <v>0.989429175475687</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9297549555059833</v>
+        <v>0.9297549555059832</v>
       </c>
     </row>
     <row r="12">
@@ -1078,7 +1078,7 @@
         <v>177585023</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01069131185162932</v>
+        <v>0.0106913118516293</v>
       </c>
       <c r="K12" t="n">
         <v>9.6</v>
@@ -1132,7 +1132,7 @@
         <v>160526628</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009660693641749242</v>
+        <v>0.0096606936417492</v>
       </c>
       <c r="K13" t="n">
         <v>9.609999999999999</v>
@@ -1186,7 +1186,7 @@
         <v>164485302</v>
       </c>
       <c r="J14" t="n">
-        <v>0.009802513949198621</v>
+        <v>0.0098025139491986</v>
       </c>
       <c r="K14" t="n">
         <v>9.550000000000001</v>
@@ -1240,7 +1240,7 @@
         <v>150195400</v>
       </c>
       <c r="J15" t="n">
-        <v>0.008909903797318217</v>
+        <v>0.0089099037973182</v>
       </c>
       <c r="K15" t="n">
         <v>9.609999999999999</v>
@@ -1294,7 +1294,7 @@
         <v>486600207</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02745260933847711</v>
+        <v>0.0274526093384771</v>
       </c>
       <c r="K16" t="n">
         <v>10.14</v>
@@ -1309,7 +1309,7 @@
         <v>10.29</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9893100097181731</v>
+        <v>0.9893100097181732</v>
       </c>
       <c r="P16" t="n">
         <v>2.635066071622162</v>
@@ -1348,7 +1348,7 @@
         <v>343495393</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01955653654818906</v>
+        <v>0.019556536548189</v>
       </c>
       <c r="K17" t="n">
         <v>10.4</v>
@@ -1363,7 +1363,7 @@
         <v>10.11</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9891196834817013</v>
+        <v>0.9891196834817012</v>
       </c>
       <c r="P17" t="n">
         <v>1.470039762007341</v>
@@ -1402,7 +1402,7 @@
         <v>207478923</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01216558796696678</v>
+        <v>0.0121655879669667</v>
       </c>
       <c r="K18" t="n">
         <v>10.07</v>
@@ -1456,7 +1456,7 @@
         <v>122624305</v>
       </c>
       <c r="J19" t="n">
-        <v>0.007234356530267869</v>
+        <v>0.0072343565302678</v>
       </c>
       <c r="K19" t="n">
         <v>9.84</v>
@@ -1474,7 +1474,7 @@
         <v>0.9897225077081192</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4644127036129767</v>
+        <v>0.4644127036129766</v>
       </c>
     </row>
     <row r="20">
@@ -1510,7 +1510,7 @@
         <v>97898890</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005803877896848019</v>
+        <v>0.005803877896848</v>
       </c>
       <c r="K20" t="n">
         <v>9.720000000000001</v>
@@ -1528,7 +1528,7 @@
         <v>0.9897330595482546</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3852864712242287</v>
+        <v>0.3852864712242286</v>
       </c>
     </row>
     <row r="21">
@@ -1564,7 +1564,7 @@
         <v>287177972</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01644392685242492</v>
+        <v>0.0164439268524249</v>
       </c>
       <c r="K21" t="n">
         <v>9.94</v>
@@ -1579,7 +1579,7 @@
         <v>10.23</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9892473118279569</v>
+        <v>0.9892473118279568</v>
       </c>
       <c r="P21" t="n">
         <v>1.138571592050779</v>
@@ -1618,7 +1618,7 @@
         <v>166419521</v>
       </c>
       <c r="J22" t="n">
-        <v>0.009484965139839416</v>
+        <v>0.0094849651398394</v>
       </c>
       <c r="K22" t="n">
         <v>10.18</v>
@@ -1633,7 +1633,7 @@
         <v>10.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9891625615763545</v>
+        <v>0.9891625615763544</v>
       </c>
       <c r="P22" t="n">
         <v>0.7748611895950992</v>
@@ -1672,7 +1672,7 @@
         <v>172801944</v>
       </c>
       <c r="J23" t="n">
-        <v>0.009798982845914709</v>
+        <v>0.009798982845914701</v>
       </c>
       <c r="K23" t="n">
         <v>10.19</v>
@@ -1687,10 +1687,10 @@
         <v>10.16</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9891732283464567</v>
+        <v>0.9891732283464568</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9581911466576809</v>
+        <v>0.9581911466576808</v>
       </c>
     </row>
     <row r="24">
@@ -1726,7 +1726,7 @@
         <v>189035880</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01063789176616902</v>
+        <v>0.010637891766169</v>
       </c>
       <c r="K24" t="n">
         <v>10.17</v>
@@ -1780,7 +1780,7 @@
         <v>198304658</v>
       </c>
       <c r="J25" t="n">
-        <v>0.01107507636793259</v>
+        <v>0.0110750763679325</v>
       </c>
       <c r="K25" t="n">
         <v>10.35</v>
@@ -1795,7 +1795,7 @@
         <v>10.37</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9893924783027965</v>
+        <v>0.9893924783027964</v>
       </c>
       <c r="P25" t="n">
         <v>1.061448326303879</v>
@@ -1834,7 +1834,7 @@
         <v>213698150</v>
       </c>
       <c r="J26" t="n">
-        <v>0.01188777737482282</v>
+        <v>0.0118877773748228</v>
       </c>
       <c r="K26" t="n">
         <v>10.43</v>
@@ -1849,7 +1849,7 @@
         <v>10.33</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9893514036786061</v>
+        <v>0.989351403678606</v>
       </c>
       <c r="P26" t="n">
         <v>1.034784376385242</v>
@@ -1888,7 +1888,7 @@
         <v>261914301</v>
       </c>
       <c r="J27" t="n">
-        <v>0.01447220135555573</v>
+        <v>0.0144722013555557</v>
       </c>
       <c r="K27" t="n">
         <v>10.34</v>
@@ -1903,7 +1903,7 @@
         <v>10.52</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9895437262357415</v>
+        <v>0.9895437262357416</v>
       </c>
       <c r="P27" t="n">
         <v>1.368278834499813</v>
@@ -1996,7 +1996,7 @@
         <v>421227008</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02225989229893175</v>
+        <v>0.0222598922989317</v>
       </c>
       <c r="K29" t="n">
         <v>10.75</v>
@@ -2050,7 +2050,7 @@
         <v>294362780</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01567153966035274</v>
+        <v>0.0156715396603527</v>
       </c>
       <c r="K30" t="n">
         <v>10.96</v>
@@ -2104,7 +2104,7 @@
         <v>243668766</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01283316548820462</v>
+        <v>0.0128331654882046</v>
       </c>
       <c r="K31" t="n">
         <v>10.89</v>
@@ -2119,7 +2119,7 @@
         <v>11</v>
       </c>
       <c r="O31" t="n">
-        <v>0.9890909090909091</v>
+        <v>0.9890909090909092</v>
       </c>
       <c r="P31" t="n">
         <v>0.7705981280133496</v>
@@ -2158,7 +2158,7 @@
         <v>304012488</v>
       </c>
       <c r="J32" t="n">
-        <v>0.01641398652123846</v>
+        <v>0.0164139865212384</v>
       </c>
       <c r="K32" t="n">
         <v>11.01</v>
@@ -2176,7 +2176,7 @@
         <v>0.9896810506566605</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9745523989556303</v>
+        <v>0.9745523989556304</v>
       </c>
     </row>
     <row r="33">
@@ -2212,7 +2212,7 @@
         <v>283188904</v>
       </c>
       <c r="J33" t="n">
-        <v>0.01581967823616171</v>
+        <v>0.0158196782361617</v>
       </c>
       <c r="K33" t="n">
         <v>10.5</v>
@@ -2266,7 +2266,7 @@
         <v>193064069</v>
       </c>
       <c r="J34" t="n">
-        <v>0.01071682326296952</v>
+        <v>0.0107168232629695</v>
       </c>
       <c r="K34" t="n">
         <v>10.41</v>
@@ -2281,7 +2281,7 @@
         <v>10.37</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9893924783027965</v>
+        <v>0.9893924783027964</v>
       </c>
       <c r="P34" t="n">
         <v>0.6456052800547801</v>
@@ -2320,7 +2320,7 @@
         <v>206209832</v>
       </c>
       <c r="J35" t="n">
-        <v>0.01174029191428377</v>
+        <v>0.0117402919142837</v>
       </c>
       <c r="K35" t="n">
         <v>10.37</v>
@@ -2335,7 +2335,7 @@
         <v>10.13</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9891411648568607</v>
+        <v>0.9891411648568608</v>
       </c>
       <c r="P35" t="n">
         <v>0.8215142520522316</v>
@@ -2374,7 +2374,7 @@
         <v>197202381</v>
       </c>
       <c r="J36" t="n">
-        <v>0.01105696962927164</v>
+        <v>0.0110569696292716</v>
       </c>
       <c r="K36" t="n">
         <v>10.13</v>
@@ -2428,7 +2428,7 @@
         <v>215672753</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01228693898237848</v>
+        <v>0.0122869389823784</v>
       </c>
       <c r="K37" t="n">
         <v>10.3</v>
@@ -2482,7 +2482,7 @@
         <v>255445821</v>
       </c>
       <c r="J38" t="n">
-        <v>0.01440648025760704</v>
+        <v>0.014406480257607</v>
       </c>
       <c r="K38" t="n">
         <v>10.14</v>
@@ -2497,7 +2497,7 @@
         <v>10.33</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9893514036786061</v>
+        <v>0.989351403678606</v>
       </c>
       <c r="P38" t="n">
         <v>1.168964307786285</v>
@@ -2536,7 +2536,7 @@
         <v>204845214</v>
       </c>
       <c r="J39" t="n">
-        <v>0.01142893873339289</v>
+        <v>0.0114289387333928</v>
       </c>
       <c r="K39" t="n">
         <v>10.39</v>
@@ -2590,7 +2590,7 @@
         <v>250886101</v>
       </c>
       <c r="J40" t="n">
-        <v>0.01405235467917259</v>
+        <v>0.0140523546791725</v>
       </c>
       <c r="K40" t="n">
         <v>10.34</v>
@@ -2605,7 +2605,7 @@
         <v>10.37</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9893924783027965</v>
+        <v>0.9893924783027964</v>
       </c>
       <c r="P40" t="n">
         <v>1.153352137669414</v>
@@ -2644,7 +2644,7 @@
         <v>1188800439</v>
       </c>
       <c r="J41" t="n">
-        <v>0.06191655919290451</v>
+        <v>0.0619165591929045</v>
       </c>
       <c r="K41" t="n">
         <v>10.5</v>
@@ -2698,7 +2698,7 @@
         <v>2723374105</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1283538058446682</v>
+        <v>0.1283538058446681</v>
       </c>
       <c r="K42" t="n">
         <v>12.02</v>
@@ -2713,7 +2713,7 @@
         <v>12.09</v>
       </c>
       <c r="O42" t="n">
-        <v>0.9892473118279571</v>
+        <v>0.9892473118279572</v>
       </c>
       <c r="P42" t="n">
         <v>5.625049303444186</v>
@@ -2767,7 +2767,7 @@
         <v>12.66</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9889415481832543</v>
+        <v>0.9889415481832544</v>
       </c>
       <c r="P43" t="n">
         <v>2.359732703463095</v>
@@ -2821,7 +2821,7 @@
         <v>13.3</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9894736842105263</v>
+        <v>0.9894736842105264</v>
       </c>
       <c r="P44" t="n">
         <v>1.592103620126075</v>
@@ -2860,7 +2860,7 @@
         <v>1964542845</v>
       </c>
       <c r="J45" t="n">
-        <v>0.08596206401185305</v>
+        <v>0.085962064011853</v>
       </c>
       <c r="K45" t="n">
         <v>13</v>
@@ -2875,7 +2875,7 @@
         <v>13</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9892307692307691</v>
+        <v>0.9892307692307692</v>
       </c>
       <c r="P45" t="n">
         <v>1.032620858957741</v>
@@ -2914,7 +2914,7 @@
         <v>1631278652</v>
       </c>
       <c r="J46" t="n">
-        <v>0.07034011830374964</v>
+        <v>0.0703401183037496</v>
       </c>
       <c r="K46" t="n">
         <v>12.8</v>
@@ -2929,7 +2929,7 @@
         <v>13.38</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9895366218236173</v>
+        <v>0.9895366218236172</v>
       </c>
       <c r="P46" t="n">
         <v>0.7204880336752194</v>
@@ -2968,7 +2968,7 @@
         <v>1339306777</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05890326177700043</v>
+        <v>0.0589032617770004</v>
       </c>
       <c r="K47" t="n">
         <v>13.22</v>
@@ -2983,7 +2983,7 @@
         <v>13.55</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9889298892988929</v>
+        <v>0.9889298892988928</v>
       </c>
       <c r="P47" t="n">
         <v>0.5931063949728806</v>
@@ -3037,7 +3037,7 @@
         <v>14.4</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9895833333333333</v>
+        <v>0.9895833333333331</v>
       </c>
       <c r="P48" t="n">
         <v>1.050869362031993</v>
@@ -3076,7 +3076,7 @@
         <v>1794399733</v>
       </c>
       <c r="J49" t="n">
-        <v>0.07500502506830821</v>
+        <v>0.0750050250683082</v>
       </c>
       <c r="K49" t="n">
         <v>14.26</v>
@@ -3091,7 +3091,7 @@
         <v>13.24</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9894259818731117</v>
+        <v>0.9894259818731116</v>
       </c>
       <c r="P49" t="n">
         <v>0.9185909278034156</v>
@@ -3130,7 +3130,7 @@
         <v>1363907007</v>
       </c>
       <c r="J50" t="n">
-        <v>0.05751861922444519</v>
+        <v>0.0575186192244451</v>
       </c>
       <c r="K50" t="n">
         <v>13.48</v>
@@ -3145,7 +3145,7 @@
         <v>13.87</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9891852919971161</v>
+        <v>0.989185291997116</v>
       </c>
       <c r="P50" t="n">
         <v>0.7568659205935486</v>
@@ -3184,7 +3184,7 @@
         <v>1071628500</v>
       </c>
       <c r="J51" t="n">
-        <v>0.045730836169255</v>
+        <v>0.0457308361692549</v>
       </c>
       <c r="K51" t="n">
         <v>14.14</v>
@@ -3238,7 +3238,7 @@
         <v>1445227132</v>
       </c>
       <c r="J52" t="n">
-        <v>0.05985734748833008</v>
+        <v>0.05985734748833</v>
       </c>
       <c r="K52" t="n">
         <v>13.56</v>
@@ -3253,10 +3253,10 @@
         <v>13.82</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9891461649782923</v>
+        <v>0.9891461649782924</v>
       </c>
       <c r="P52" t="n">
-        <v>0.9154565847955487</v>
+        <v>0.9154565847955488</v>
       </c>
     </row>
     <row r="53">
@@ -3292,7 +3292,7 @@
         <v>1183585135</v>
       </c>
       <c r="J53" t="n">
-        <v>0.05177542666963392</v>
+        <v>0.0517754266696339</v>
       </c>
       <c r="K53" t="n">
         <v>13.76</v>
@@ -3307,7 +3307,7 @@
         <v>12.95</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9891891891891893</v>
+        <v>0.9891891891891892</v>
       </c>
       <c r="P53" t="n">
         <v>0.7895477374522279</v>
@@ -3346,7 +3346,7 @@
         <v>857949161</v>
       </c>
       <c r="J54" t="n">
-        <v>0.03827958057849067</v>
+        <v>0.0382795805784906</v>
       </c>
       <c r="K54" t="n">
         <v>13.13</v>
@@ -3361,7 +3361,7 @@
         <v>13.03</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9892555640828857</v>
+        <v>0.9892555640828856</v>
       </c>
       <c r="P54" t="n">
         <v>0.6602494585122977</v>
@@ -3400,7 +3400,7 @@
         <v>872328634</v>
       </c>
       <c r="J55" t="n">
-        <v>0.04033001080405956</v>
+        <v>0.0403300108040595</v>
       </c>
       <c r="K55" t="n">
         <v>13.01</v>
@@ -3454,7 +3454,7 @@
         <v>807336874</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03806376676533375</v>
+        <v>0.0380637667653337</v>
       </c>
       <c r="K56" t="n">
         <v>12.25</v>
@@ -3508,7 +3508,7 @@
         <v>898675472</v>
       </c>
       <c r="J57" t="n">
-        <v>0.04125618610579895</v>
+        <v>0.0412561861057989</v>
       </c>
       <c r="K57" t="n">
         <v>12.32</v>
@@ -3526,7 +3526,7 @@
         <v>0.988888888888889</v>
       </c>
       <c r="P57" t="n">
-        <v>0.9035277696906213</v>
+        <v>0.9035277696906212</v>
       </c>
     </row>
     <row r="58">
@@ -3562,7 +3562,7 @@
         <v>1535733128</v>
       </c>
       <c r="J58" t="n">
-        <v>0.06523728473468941</v>
+        <v>0.0652372847346894</v>
       </c>
       <c r="K58" t="n">
         <v>12.61</v>
@@ -3670,7 +3670,7 @@
         <v>962511687</v>
       </c>
       <c r="J60" t="n">
-        <v>0.04352807909989294</v>
+        <v>0.0435280790998929</v>
       </c>
       <c r="K60" t="n">
         <v>12.9</v>
@@ -3685,7 +3685,7 @@
         <v>12.64</v>
       </c>
       <c r="O60" t="n">
-        <v>0.9889240506329113</v>
+        <v>0.9889240506329112</v>
       </c>
       <c r="P60" t="n">
         <v>0.8380932187753741</v>
@@ -3724,7 +3724,7 @@
         <v>732634569</v>
       </c>
       <c r="J61" t="n">
-        <v>0.03564438079033002</v>
+        <v>0.03564438079033</v>
       </c>
       <c r="K61" t="n">
         <v>12</v>
@@ -3778,7 +3778,7 @@
         <v>787213667</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03828854890978334</v>
+        <v>0.0382885489097833</v>
       </c>
       <c r="K62" t="n">
         <v>11.75</v>
@@ -3832,7 +3832,7 @@
         <v>581530734</v>
       </c>
       <c r="J63" t="n">
-        <v>0.02878079820373378</v>
+        <v>0.0287807982037337</v>
       </c>
       <c r="K63" t="n">
         <v>11.98</v>
@@ -3886,7 +3886,7 @@
         <v>542596765</v>
       </c>
       <c r="J64" t="n">
-        <v>0.02703225532631744</v>
+        <v>0.0270322553263174</v>
       </c>
       <c r="K64" t="n">
         <v>11.6</v>
@@ -3940,7 +3940,7 @@
         <v>1454365938</v>
       </c>
       <c r="J65" t="n">
-        <v>0.06836936524865964</v>
+        <v>0.06836936524865959</v>
       </c>
       <c r="K65" t="n">
         <v>11.78</v>
@@ -4048,7 +4048,7 @@
         <v>1277886044</v>
       </c>
       <c r="J67" t="n">
-        <v>0.05827425855099107</v>
+        <v>0.058274258550991</v>
       </c>
       <c r="K67" t="n">
         <v>12.46</v>
@@ -4102,7 +4102,7 @@
         <v>988626726</v>
       </c>
       <c r="J68" t="n">
-        <v>0.04647768649642465</v>
+        <v>0.0464776864964246</v>
       </c>
       <c r="K68" t="n">
         <v>12.56</v>
@@ -4156,7 +4156,7 @@
         <v>1660738153</v>
       </c>
       <c r="J69" t="n">
-        <v>0.07529403117844916</v>
+        <v>0.0752940311784491</v>
       </c>
       <c r="K69" t="n">
         <v>12.18</v>
@@ -4210,7 +4210,7 @@
         <v>1484083721</v>
       </c>
       <c r="J70" t="n">
-        <v>0.06804105247488304</v>
+        <v>0.068041052474883</v>
       </c>
       <c r="K70" t="n">
         <v>13.01</v>
@@ -4264,7 +4264,7 @@
         <v>1279699368</v>
       </c>
       <c r="J71" t="n">
-        <v>0.05991741384601006</v>
+        <v>0.05991741384601</v>
       </c>
       <c r="K71" t="n">
         <v>12.97</v>
@@ -4372,7 +4372,7 @@
         <v>896121621</v>
       </c>
       <c r="J73" t="n">
-        <v>0.04638455249033133</v>
+        <v>0.0463845524903313</v>
       </c>
       <c r="K73" t="n">
         <v>11.45</v>
@@ -4426,7 +4426,7 @@
         <v>655388723</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03563364227947496</v>
+        <v>0.0356336422794749</v>
       </c>
       <c r="K74" t="n">
         <v>11.24</v>
@@ -4480,7 +4480,7 @@
         <v>664575937</v>
       </c>
       <c r="J75" t="n">
-        <v>0.03654485609297191</v>
+        <v>0.0365448560929719</v>
       </c>
       <c r="K75" t="n">
         <v>10.3</v>
@@ -4534,7 +4534,7 @@
         <v>719120374</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03977828285782877</v>
+        <v>0.0397782828578287</v>
       </c>
       <c r="K76" t="n">
         <v>10.4</v>
@@ -4588,7 +4588,7 @@
         <v>992525819</v>
       </c>
       <c r="J77" t="n">
-        <v>0.05060391431487942</v>
+        <v>0.0506039143148794</v>
       </c>
       <c r="K77" t="n">
         <v>11.19</v>
@@ -4642,7 +4642,7 @@
         <v>958217945</v>
       </c>
       <c r="J78" t="n">
-        <v>0.04830504343716071</v>
+        <v>0.0483050434371607</v>
       </c>
       <c r="K78" t="n">
         <v>11.13</v>
@@ -4660,7 +4660,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="n">
-        <v>1.155925867932559</v>
+        <v>1.15592586793256</v>
       </c>
     </row>
     <row r="79">
@@ -4696,7 +4696,7 @@
         <v>650733514</v>
       </c>
       <c r="J79" t="n">
-        <v>0.03304815792647479</v>
+        <v>0.0330481579264747</v>
       </c>
       <c r="K79" t="n">
         <v>11.4</v>
@@ -4750,7 +4750,7 @@
         <v>600330871</v>
       </c>
       <c r="J80" t="n">
-        <v>0.03060440595043592</v>
+        <v>0.0306044059504359</v>
       </c>
       <c r="K80" t="n">
         <v>11.33</v>
@@ -4804,7 +4804,7 @@
         <v>449183460</v>
       </c>
       <c r="J81" t="n">
-        <v>0.02349210272250418</v>
+        <v>0.0234921027225041</v>
       </c>
       <c r="K81" t="n">
         <v>11.27</v>
@@ -4858,7 +4858,7 @@
         <v>472832724</v>
       </c>
       <c r="J82" t="n">
-        <v>0.02606612545208296</v>
+        <v>0.0260661254520829</v>
       </c>
       <c r="K82" t="n">
         <v>10.99</v>
@@ -4912,7 +4912,7 @@
         <v>670337713</v>
       </c>
       <c r="J83" t="n">
-        <v>0.03695547990243902</v>
+        <v>0.036955479902439</v>
       </c>
       <c r="K83" t="n">
         <v>10.32</v>
@@ -4966,7 +4966,7 @@
         <v>423693909</v>
       </c>
       <c r="J84" t="n">
-        <v>0.02252041587281995</v>
+        <v>0.0225204158728199</v>
       </c>
       <c r="K84" t="n">
         <v>10.79</v>
@@ -5020,7 +5020,7 @@
         <v>377490778</v>
       </c>
       <c r="J85" t="n">
-        <v>0.02093382417820963</v>
+        <v>0.0209338241782096</v>
       </c>
       <c r="K85" t="n">
         <v>10.55</v>
@@ -5074,7 +5074,7 @@
         <v>363507901</v>
       </c>
       <c r="J86" t="n">
-        <v>0.02078931620597371</v>
+        <v>0.0207893162059737</v>
       </c>
       <c r="K86" t="n">
         <v>10.14</v>
@@ -5128,7 +5128,7 @@
         <v>373835756</v>
       </c>
       <c r="J87" t="n">
-        <v>0.02110287343396676</v>
+        <v>0.0211028734339667</v>
       </c>
       <c r="K87" t="n">
         <v>10.25</v>
@@ -5182,7 +5182,7 @@
         <v>373275568</v>
       </c>
       <c r="J88" t="n">
-        <v>0.02125599280913262</v>
+        <v>0.0212559928091326</v>
       </c>
       <c r="K88" t="n">
         <v>10.2</v>
@@ -5236,7 +5236,7 @@
         <v>446704812</v>
       </c>
       <c r="J89" t="n">
-        <v>0.02611730215311748</v>
+        <v>0.0261173021531174</v>
       </c>
       <c r="K89" t="n">
         <v>10.02</v>
@@ -5290,7 +5290,7 @@
         <v>362125120</v>
       </c>
       <c r="J90" t="n">
-        <v>0.02231547535870047</v>
+        <v>0.0223154753587004</v>
       </c>
       <c r="K90" t="n">
         <v>9.720000000000001</v>
@@ -5344,7 +5344,7 @@
         <v>365418940</v>
       </c>
       <c r="J91" t="n">
-        <v>0.02244579296993469</v>
+        <v>0.0224457929699346</v>
       </c>
       <c r="K91" t="n">
         <v>9.26</v>
@@ -5362,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>1.005807486232504</v>
+        <v>1.005807486232503</v>
       </c>
     </row>
     <row r="92">
@@ -5398,7 +5398,7 @@
         <v>300044284</v>
       </c>
       <c r="J92" t="n">
-        <v>0.01780554723633831</v>
+        <v>0.0178055472363383</v>
       </c>
       <c r="K92" t="n">
         <v>9.59</v>
@@ -5452,7 +5452,7 @@
         <v>228149221</v>
       </c>
       <c r="J93" t="n">
-        <v>0.01344020807481951</v>
+        <v>0.0134402080748195</v>
       </c>
       <c r="K93" t="n">
         <v>9.630000000000001</v>
@@ -5506,7 +5506,7 @@
         <v>219337118</v>
       </c>
       <c r="J94" t="n">
-        <v>0.01327575665800414</v>
+        <v>0.0132757566580041</v>
       </c>
       <c r="K94" t="n">
         <v>9.699999999999999</v>
@@ -5560,7 +5560,7 @@
         <v>227541156</v>
       </c>
       <c r="J95" t="n">
-        <v>0.01351477312869947</v>
+        <v>0.0135147731286994</v>
       </c>
       <c r="K95" t="n">
         <v>9.550000000000001</v>
@@ -5614,7 +5614,7 @@
         <v>174944670</v>
       </c>
       <c r="J96" t="n">
-        <v>0.01048576855087454</v>
+        <v>0.0104857685508745</v>
       </c>
       <c r="K96" t="n">
         <v>9.699999999999999</v>
@@ -5668,7 +5668,7 @@
         <v>376584591</v>
       </c>
       <c r="J97" t="n">
-        <v>0.02193926245154992</v>
+        <v>0.0219392624515499</v>
       </c>
       <c r="K97" t="n">
         <v>9.65</v>
@@ -5722,7 +5722,7 @@
         <v>298488541</v>
       </c>
       <c r="J98" t="n">
-        <v>0.01753103288051672</v>
+        <v>0.0175310328805167</v>
       </c>
       <c r="K98" t="n">
         <v>9.949999999999999</v>
@@ -5776,7 +5776,7 @@
         <v>265283500</v>
       </c>
       <c r="J99" t="n">
-        <v>0.01540541688124092</v>
+        <v>0.0154054168812409</v>
       </c>
       <c r="K99" t="n">
         <v>10</v>
@@ -5794,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>1.003654764637075</v>
+        <v>1.003654764637076</v>
       </c>
     </row>
     <row r="100">
@@ -5830,7 +5830,7 @@
         <v>167445936</v>
       </c>
       <c r="J100" t="n">
-        <v>0.009739176808758616</v>
+        <v>0.0097391768087586</v>
       </c>
       <c r="K100" t="n">
         <v>9.84</v>
@@ -5884,7 +5884,7 @@
         <v>233671365</v>
       </c>
       <c r="J101" t="n">
-        <v>0.01335587521639353</v>
+        <v>0.0133558752163935</v>
       </c>
       <c r="K101" t="n">
         <v>9.960000000000001</v>
@@ -5938,7 +5938,7 @@
         <v>279004852</v>
       </c>
       <c r="J102" t="n">
-        <v>0.01553995573439236</v>
+        <v>0.0155399557343923</v>
       </c>
       <c r="K102" t="n">
         <v>10.24</v>
@@ -5992,7 +5992,7 @@
         <v>295178900</v>
       </c>
       <c r="J103" t="n">
-        <v>0.01650252789480048</v>
+        <v>0.0165025278948004</v>
       </c>
       <c r="K103" t="n">
         <v>10.53</v>
@@ -6100,7 +6100,7 @@
         <v>261045144</v>
       </c>
       <c r="J105" t="n">
-        <v>0.01447437532117515</v>
+        <v>0.0144743753211751</v>
       </c>
       <c r="K105" t="n">
         <v>10.56</v>
@@ -6154,7 +6154,7 @@
         <v>217048168</v>
       </c>
       <c r="J106" t="n">
-        <v>0.01221077035407143</v>
+        <v>0.0122107703540714</v>
       </c>
       <c r="K106" t="n">
         <v>10.36</v>
@@ -6208,7 +6208,7 @@
         <v>155775404</v>
       </c>
       <c r="J107" t="n">
-        <v>0.008815156960956954</v>
+        <v>0.0088151569609569</v>
       </c>
       <c r="K107" t="n">
         <v>10.18</v>
@@ -6262,7 +6262,7 @@
         <v>266420998</v>
       </c>
       <c r="J108" t="n">
-        <v>0.01531626751463312</v>
+        <v>0.0153162675146331</v>
       </c>
       <c r="K108" t="n">
         <v>10.23</v>
@@ -6316,7 +6316,7 @@
         <v>636052606</v>
       </c>
       <c r="J109" t="n">
-        <v>0.03424924558519227</v>
+        <v>0.0342492455851922</v>
       </c>
       <c r="K109" t="n">
         <v>10.1</v>
@@ -6370,7 +6370,7 @@
         <v>1535040772</v>
       </c>
       <c r="J110" t="n">
-        <v>0.07735375195427029</v>
+        <v>0.0773537519542702</v>
       </c>
       <c r="K110" t="n">
         <v>11.29</v>
@@ -6424,7 +6424,7 @@
         <v>1072241949</v>
       </c>
       <c r="J111" t="n">
-        <v>0.05277038443868282</v>
+        <v>0.0527703844386828</v>
       </c>
       <c r="K111" t="n">
         <v>11.75</v>
@@ -6478,7 +6478,7 @@
         <v>2615213529</v>
       </c>
       <c r="J112" t="n">
-        <v>0.1179636455018439</v>
+        <v>0.1179636455018438</v>
       </c>
       <c r="K112" t="n">
         <v>11.89</v>
@@ -6532,7 +6532,7 @@
         <v>1905394843</v>
       </c>
       <c r="J113" t="n">
-        <v>0.08635243199211207</v>
+        <v>0.086352431992112</v>
       </c>
       <c r="K113" t="n">
         <v>12.83</v>
@@ -6586,7 +6586,7 @@
         <v>1401406868</v>
       </c>
       <c r="J114" t="n">
-        <v>0.06138113541032933</v>
+        <v>0.0613811354103293</v>
       </c>
       <c r="K114" t="n">
         <v>12.86</v>
@@ -6640,7 +6640,7 @@
         <v>1271106722</v>
       </c>
       <c r="J115" t="n">
-        <v>0.05543506870786812</v>
+        <v>0.0554350687078681</v>
       </c>
       <c r="K115" t="n">
         <v>13.1</v>
@@ -6694,7 +6694,7 @@
         <v>978161080</v>
       </c>
       <c r="J116" t="n">
-        <v>0.04236031015427182</v>
+        <v>0.0423603101542718</v>
       </c>
       <c r="K116" t="n">
         <v>13.12</v>
@@ -6748,7 +6748,7 @@
         <v>777599360</v>
       </c>
       <c r="J117" t="n">
-        <v>0.03369374241287517</v>
+        <v>0.0336937424128751</v>
       </c>
       <c r="K117" t="n">
         <v>13.46</v>
@@ -6802,7 +6802,7 @@
         <v>884540012</v>
       </c>
       <c r="J118" t="n">
-        <v>0.03850909477157433</v>
+        <v>0.0385090947715743</v>
       </c>
       <c r="K118" t="n">
         <v>13.17</v>
@@ -6856,7 +6856,7 @@
         <v>597568658</v>
       </c>
       <c r="J119" t="n">
-        <v>0.02644063181357697</v>
+        <v>0.0264406318135769</v>
       </c>
       <c r="K119" t="n">
         <v>13.3</v>
@@ -6910,7 +6910,7 @@
         <v>753175705</v>
       </c>
       <c r="J120" t="n">
-        <v>0.03325841129324163</v>
+        <v>0.0332584112932416</v>
       </c>
       <c r="K120" t="n">
         <v>12.63</v>
@@ -6964,7 +6964,7 @@
         <v>556790078</v>
       </c>
       <c r="J121" t="n">
-        <v>0.02385972447387665</v>
+        <v>0.0238597244738766</v>
       </c>
       <c r="K121" t="n">
         <v>13.6</v>
@@ -7018,7 +7018,7 @@
         <v>57961806</v>
       </c>
       <c r="J122" t="n">
-        <v>0.01637704393170675</v>
+        <v>0.0163770439317067</v>
       </c>
       <c r="K122" t="n">
         <v>14.58</v>
@@ -7072,7 +7072,7 @@
         <v>71611728</v>
       </c>
       <c r="J123" t="n">
-        <v>0.02027368045803801</v>
+        <v>0.020273680458038</v>
       </c>
       <c r="K123" t="n">
         <v>14.51</v>
@@ -7126,7 +7126,7 @@
         <v>74640040</v>
       </c>
       <c r="J124" t="n">
-        <v>0.02106621670068165</v>
+        <v>0.0210662167006816</v>
       </c>
       <c r="K124" t="n">
         <v>14.3</v>
@@ -7180,7 +7180,7 @@
         <v>67152705</v>
       </c>
       <c r="J125" t="n">
-        <v>0.01886860012868033</v>
+        <v>0.0188686001286803</v>
       </c>
       <c r="K125" t="n">
         <v>14.38</v>
@@ -7195,7 +7195,7 @@
         <v>14.46</v>
       </c>
       <c r="O125" t="n">
-        <v>0.9910096818810511</v>
+        <v>0.9910096818810512</v>
       </c>
       <c r="P125" t="n">
         <v>0.9345506604905116</v>
@@ -7288,7 +7288,7 @@
         <v>63759406</v>
       </c>
       <c r="J127" t="n">
-        <v>0.01835186160627764</v>
+        <v>0.0183518616062776</v>
       </c>
       <c r="K127" t="n">
         <v>14.33</v>
@@ -7303,7 +7303,7 @@
         <v>14.29</v>
       </c>
       <c r="O127" t="n">
-        <v>0.9909027291812457</v>
+        <v>0.9909027291812456</v>
       </c>
       <c r="P127" t="n">
         <v>0.9735056801347748</v>
@@ -7342,7 +7342,7 @@
         <v>67929895</v>
       </c>
       <c r="J128" t="n">
-        <v>0.01972779258308953</v>
+        <v>0.0197277925830895</v>
       </c>
       <c r="K128" t="n">
         <v>14.25</v>
@@ -7357,10 +7357,10 @@
         <v>13.98</v>
       </c>
       <c r="O128" t="n">
-        <v>0.9914163090128755</v>
+        <v>0.9914163090128756</v>
       </c>
       <c r="P128" t="n">
-        <v>1.02501858759683</v>
+        <v>1.025018587596831</v>
       </c>
     </row>
     <row r="129">
@@ -7396,7 +7396,7 @@
         <v>80600923</v>
       </c>
       <c r="J129" t="n">
-        <v>0.02390233047524408</v>
+        <v>0.023902330475244</v>
       </c>
       <c r="K129" t="n">
         <v>13.97</v>
@@ -7450,7 +7450,7 @@
         <v>142631364</v>
       </c>
       <c r="J130" t="n">
-        <v>0.04471490296361957</v>
+        <v>0.0447149029636195</v>
       </c>
       <c r="K130" t="n">
         <v>13.33</v>
@@ -7465,7 +7465,7 @@
         <v>12.78</v>
       </c>
       <c r="O130" t="n">
-        <v>0.9913928012519563</v>
+        <v>0.9913928012519564</v>
       </c>
       <c r="P130" t="n">
         <v>2.269294042559249</v>
@@ -7504,7 +7504,7 @@
         <v>120958478</v>
       </c>
       <c r="J131" t="n">
-        <v>0.03752744722400667</v>
+        <v>0.0375274472240066</v>
       </c>
       <c r="K131" t="n">
         <v>13.02</v>
@@ -7522,7 +7522,7 @@
         <v>0.9909977494373594</v>
       </c>
       <c r="P131" t="n">
-        <v>1.508726999946502</v>
+        <v>1.508726999946503</v>
       </c>
     </row>
     <row r="132">
@@ -7558,7 +7558,7 @@
         <v>58792180</v>
       </c>
       <c r="J132" t="n">
-        <v>0.01792705565728861</v>
+        <v>0.0179270556572886</v>
       </c>
       <c r="K132" t="n">
         <v>13.39</v>
@@ -7612,7 +7612,7 @@
         <v>61748500</v>
       </c>
       <c r="J133" t="n">
-        <v>0.01882792964742203</v>
+        <v>0.018827929647422</v>
       </c>
       <c r="K133" t="n">
         <v>13.39</v>
@@ -7666,7 +7666,7 @@
         <v>120707792</v>
       </c>
       <c r="J134" t="n">
-        <v>0.03594706309612185</v>
+        <v>0.0359470630961218</v>
       </c>
       <c r="K134" t="n">
         <v>13.2</v>
@@ -7681,7 +7681,7 @@
         <v>13.9</v>
       </c>
       <c r="O134" t="n">
-        <v>0.9913669064748201</v>
+        <v>0.99136690647482</v>
       </c>
       <c r="P134" t="n">
         <v>1.257772817477299</v>
@@ -7720,7 +7720,7 @@
         <v>80827766</v>
       </c>
       <c r="J135" t="n">
-        <v>0.02365683992798569</v>
+        <v>0.0236568399279856</v>
       </c>
       <c r="K135" t="n">
         <v>13.8</v>
@@ -7774,7 +7774,7 @@
         <v>75164755</v>
       </c>
       <c r="J136" t="n">
-        <v>0.02186751813325166</v>
+        <v>0.0218675181332516</v>
       </c>
       <c r="K136" t="n">
         <v>13.95</v>
@@ -7789,7 +7789,7 @@
         <v>13.81</v>
       </c>
       <c r="O136" t="n">
-        <v>0.9913106444605357</v>
+        <v>0.9913106444605356</v>
       </c>
       <c r="P136" t="n">
         <v>0.8166448817558319</v>
@@ -7828,7 +7828,7 @@
         <v>88861793</v>
       </c>
       <c r="J137" t="n">
-        <v>0.02579330401212871</v>
+        <v>0.0257933040121287</v>
       </c>
       <c r="K137" t="n">
         <v>13.99</v>
@@ -7843,7 +7843,7 @@
         <v>14.15</v>
       </c>
       <c r="O137" t="n">
-        <v>0.9908127208480565</v>
+        <v>0.9908127208480564</v>
       </c>
       <c r="P137" t="n">
         <v>1.090843610323379</v>
@@ -7882,7 +7882,7 @@
         <v>106130288</v>
       </c>
       <c r="J138" t="n">
-        <v>0.03050408399348022</v>
+        <v>0.0305040839934802</v>
       </c>
       <c r="K138" t="n">
         <v>14.17</v>
@@ -7936,7 +7936,7 @@
         <v>81595075</v>
       </c>
       <c r="J139" t="n">
-        <v>0.02413811408426308</v>
+        <v>0.024138114084263</v>
       </c>
       <c r="K139" t="n">
         <v>14.1</v>
@@ -7951,7 +7951,7 @@
         <v>13.63</v>
       </c>
       <c r="O139" t="n">
-        <v>0.9911958914159941</v>
+        <v>0.991195891415994</v>
       </c>
       <c r="P139" t="n">
         <v>0.876036972044589</v>
@@ -7990,7 +7990,7 @@
         <v>75910672</v>
       </c>
       <c r="J140" t="n">
-        <v>0.02252898421025233</v>
+        <v>0.0225289842102523</v>
       </c>
       <c r="K140" t="n">
         <v>13.67</v>
@@ -8044,7 +8044,7 @@
         <v>112939604</v>
       </c>
       <c r="J141" t="n">
-        <v>0.03288659715093739</v>
+        <v>0.0328865971509373</v>
       </c>
       <c r="K141" t="n">
         <v>13.95</v>
@@ -8059,7 +8059,7 @@
         <v>14.13</v>
       </c>
       <c r="O141" t="n">
-        <v>0.9907997169143665</v>
+        <v>0.9907997169143664</v>
       </c>
       <c r="P141" t="n">
         <v>1.317234202086744</v>
@@ -8098,7 +8098,7 @@
         <v>114748283</v>
       </c>
       <c r="J142" t="n">
-        <v>0.03322945468936377</v>
+        <v>0.0332294546893637</v>
       </c>
       <c r="K142" t="n">
         <v>13.97</v>
@@ -8116,7 +8116,7 @@
         <v>0.991404011461318</v>
       </c>
       <c r="P142" t="n">
-        <v>1.223010293522399</v>
+        <v>1.223010293522398</v>
       </c>
     </row>
     <row r="143">
@@ -8152,7 +8152,7 @@
         <v>78811395</v>
       </c>
       <c r="J143" t="n">
-        <v>0.02302228909930772</v>
+        <v>0.0230222890993077</v>
       </c>
       <c r="K143" t="n">
         <v>13.96</v>
@@ -8167,7 +8167,7 @@
         <v>13.9</v>
       </c>
       <c r="O143" t="n">
-        <v>0.9913669064748201</v>
+        <v>0.99136690647482</v>
       </c>
       <c r="P143" t="n">
         <v>0.8033614871333888</v>
@@ -8206,7 +8206,7 @@
         <v>68068763</v>
       </c>
       <c r="J144" t="n">
-        <v>0.02006963499021746</v>
+        <v>0.0200696349902174</v>
       </c>
       <c r="K144" t="n">
         <v>13.9</v>
@@ -8221,7 +8221,7 @@
         <v>13.98</v>
       </c>
       <c r="O144" t="n">
-        <v>0.9914163090128755</v>
+        <v>0.9914163090128756</v>
       </c>
       <c r="P144" t="n">
         <v>0.7389113095690535</v>
@@ -8260,7 +8260,7 @@
         <v>80254863</v>
       </c>
       <c r="J145" t="n">
-        <v>0.02377323349654267</v>
+        <v>0.0237732334965426</v>
       </c>
       <c r="K145" t="n">
         <v>14.02</v>
@@ -8275,7 +8275,7 @@
         <v>13.81</v>
       </c>
       <c r="O145" t="n">
-        <v>0.9913106444605357</v>
+        <v>0.9913106444605356</v>
       </c>
       <c r="P145" t="n">
         <v>0.9022993042827194</v>
@@ -8314,7 +8314,7 @@
         <v>123914673</v>
       </c>
       <c r="J146" t="n">
-        <v>0.03609930017622884</v>
+        <v>0.0360993001762288</v>
       </c>
       <c r="K146" t="n">
         <v>13.97</v>
@@ -8368,7 +8368,7 @@
         <v>112539566</v>
       </c>
       <c r="J147" t="n">
-        <v>0.03298078013590423</v>
+        <v>0.0329807801359042</v>
       </c>
       <c r="K147" t="n">
         <v>13.99</v>
@@ -8383,7 +8383,7 @@
         <v>14.09</v>
       </c>
       <c r="O147" t="n">
-        <v>0.9907735982966643</v>
+        <v>0.9907735982966644</v>
       </c>
       <c r="P147" t="n">
         <v>1.210802287055604</v>
@@ -8422,7 +8422,7 @@
         <v>148915260</v>
       </c>
       <c r="J148" t="n">
-        <v>0.04446686847286628</v>
+        <v>0.0444668684728662</v>
       </c>
       <c r="K148" t="n">
         <v>13.98</v>
@@ -8476,7 +8476,7 @@
         <v>85012248</v>
       </c>
       <c r="J149" t="n">
-        <v>0.02537008395099147</v>
+        <v>0.0253700839509914</v>
       </c>
       <c r="K149" t="n">
         <v>13.64</v>
@@ -8491,7 +8491,7 @@
         <v>13.68</v>
       </c>
       <c r="O149" t="n">
-        <v>0.9912280701754387</v>
+        <v>0.9912280701754388</v>
       </c>
       <c r="P149" t="n">
         <v>0.8059633205871837</v>
@@ -8584,7 +8584,7 @@
         <v>71678900</v>
       </c>
       <c r="J151" t="n">
-        <v>0.02193061934705638</v>
+        <v>0.0219306193470563</v>
       </c>
       <c r="K151" t="n">
         <v>13.46</v>
@@ -8638,7 +8638,7 @@
         <v>57469748</v>
       </c>
       <c r="J152" t="n">
-        <v>0.01778707761258095</v>
+        <v>0.0177870776125809</v>
       </c>
       <c r="K152" t="n">
         <v>13.38</v>
@@ -8653,7 +8653,7 @@
         <v>13.16</v>
       </c>
       <c r="O152" t="n">
-        <v>0.9908814589665653</v>
+        <v>0.9908814589665652</v>
       </c>
       <c r="P152" t="n">
         <v>0.6074922341178841</v>
@@ -8692,7 +8692,7 @@
         <v>86993180</v>
       </c>
       <c r="J153" t="n">
-        <v>0.02749109683986896</v>
+        <v>0.0274910968398689</v>
       </c>
       <c r="K153" t="n">
         <v>13.12</v>
@@ -8707,7 +8707,7 @@
         <v>12.92</v>
       </c>
       <c r="O153" t="n">
-        <v>0.9914860681114551</v>
+        <v>0.9914860681114552</v>
       </c>
       <c r="P153" t="n">
         <v>1.047648097449333</v>
@@ -8746,7 +8746,7 @@
         <v>83534244</v>
       </c>
       <c r="J154" t="n">
-        <v>0.02638648314435428</v>
+        <v>0.0263864831443542</v>
       </c>
       <c r="K154" t="n">
         <v>12.9</v>
@@ -8800,7 +8800,7 @@
         <v>57008895</v>
       </c>
       <c r="J155" t="n">
-        <v>0.01786386475316836</v>
+        <v>0.0178638647531683</v>
       </c>
       <c r="K155" t="n">
         <v>13.09</v>
@@ -8815,7 +8815,7 @@
         <v>13.01</v>
       </c>
       <c r="O155" t="n">
-        <v>0.9907763259031515</v>
+        <v>0.9907763259031516</v>
       </c>
       <c r="P155" t="n">
         <v>0.7750419854206215</v>
@@ -8854,7 +8854,7 @@
         <v>66437915</v>
       </c>
       <c r="J156" t="n">
-        <v>0.02050605991189957</v>
+        <v>0.0205060599118995</v>
       </c>
       <c r="K156" t="n">
         <v>12.83</v>
@@ -8872,7 +8872,7 @@
         <v>0.9909228441754916</v>
       </c>
       <c r="P156" t="n">
-        <v>0.9198913431273167</v>
+        <v>0.9198913431273168</v>
       </c>
     </row>
     <row r="157">
@@ -8908,7 +8908,7 @@
         <v>242789323</v>
       </c>
       <c r="J157" t="n">
-        <v>0.07145693890287962</v>
+        <v>0.0714569389028796</v>
       </c>
       <c r="K157" t="n">
         <v>13.5</v>
@@ -8962,7 +8962,7 @@
         <v>120490409</v>
       </c>
       <c r="J158" t="n">
-        <v>0.03548965064060677</v>
+        <v>0.0354896506406067</v>
       </c>
       <c r="K158" t="n">
         <v>13.84</v>
@@ -9016,7 +9016,7 @@
         <v>94467421</v>
       </c>
       <c r="J159" t="n">
-        <v>0.02780710435929301</v>
+        <v>0.027807104359293</v>
       </c>
       <c r="K159" t="n">
         <v>13.86</v>
@@ -9070,7 +9070,7 @@
         <v>86322543</v>
       </c>
       <c r="J160" t="n">
-        <v>0.02519533460168757</v>
+        <v>0.0251953346016875</v>
       </c>
       <c r="K160" t="n">
         <v>13.86</v>
@@ -9124,7 +9124,7 @@
         <v>129481167</v>
       </c>
       <c r="J161" t="n">
-        <v>0.03742980708505957</v>
+        <v>0.0374298070850595</v>
       </c>
       <c r="K161" t="n">
         <v>13.98</v>
@@ -9139,7 +9139,7 @@
         <v>14.18</v>
       </c>
       <c r="O161" t="n">
-        <v>0.9908321579689705</v>
+        <v>0.9908321579689704</v>
       </c>
       <c r="P161" t="n">
         <v>1.037094808839562</v>
@@ -9178,7 +9178,7 @@
         <v>135248509</v>
       </c>
       <c r="J162" t="n">
-        <v>0.03991993639064979</v>
+        <v>0.0399199363906497</v>
       </c>
       <c r="K162" t="n">
         <v>14.11</v>
@@ -9193,7 +9193,7 @@
         <v>13.74</v>
       </c>
       <c r="O162" t="n">
-        <v>0.9912663755458515</v>
+        <v>0.9912663755458516</v>
       </c>
       <c r="P162" t="n">
         <v>1.011251694524842</v>
@@ -9232,7 +9232,7 @@
         <v>114835894</v>
       </c>
       <c r="J163" t="n">
-        <v>0.03430002275647147</v>
+        <v>0.0343000227564714</v>
       </c>
       <c r="K163" t="n">
         <v>13.68</v>
@@ -9250,7 +9250,7 @@
         <v>0.9911634756995582</v>
       </c>
       <c r="P163" t="n">
-        <v>1.034118536922004</v>
+        <v>1.034118536922005</v>
       </c>
     </row>
     <row r="164">
@@ -9286,7 +9286,7 @@
         <v>96244629</v>
       </c>
       <c r="J164" t="n">
-        <v>0.02917605579882401</v>
+        <v>0.029176055798824</v>
       </c>
       <c r="K164" t="n">
         <v>13.58</v>
@@ -9340,7 +9340,7 @@
         <v>107914763</v>
       </c>
       <c r="J165" t="n">
-        <v>0.03350137126504199</v>
+        <v>0.0335013712650419</v>
       </c>
       <c r="K165" t="n">
         <v>13.32</v>
@@ -9355,7 +9355,7 @@
         <v>13.06</v>
       </c>
       <c r="O165" t="n">
-        <v>0.9908116385911179</v>
+        <v>0.990811638591118</v>
       </c>
       <c r="P165" t="n">
         <v>1.008948857619421</v>
@@ -9394,7 +9394,7 @@
         <v>143096789</v>
       </c>
       <c r="J166" t="n">
-        <v>0.04606188842951186</v>
+        <v>0.0460618884295118</v>
       </c>
       <c r="K166" t="n">
         <v>13.06</v>
@@ -9409,7 +9409,7 @@
         <v>12.64</v>
       </c>
       <c r="O166" t="n">
-        <v>0.9912974683544303</v>
+        <v>0.9912974683544304</v>
       </c>
       <c r="P166" t="n">
         <v>1.321133196680577</v>
@@ -9448,7 +9448,7 @@
         <v>96817586</v>
       </c>
       <c r="J167" t="n">
-        <v>0.03096007771127699</v>
+        <v>0.0309600777112769</v>
       </c>
       <c r="K167" t="n">
         <v>12.7</v>
@@ -9463,7 +9463,7 @@
         <v>12.82</v>
       </c>
       <c r="O167" t="n">
-        <v>0.9914196567862715</v>
+        <v>0.9914196567862716</v>
       </c>
       <c r="P167" t="n">
         <v>0.8460920544233451</v>
@@ -9502,7 +9502,7 @@
         <v>80662711</v>
       </c>
       <c r="J168" t="n">
-        <v>0.02619906707639867</v>
+        <v>0.0261990670763986</v>
       </c>
       <c r="K168" t="n">
         <v>12.75</v>
@@ -9517,7 +9517,7 @@
         <v>12.57</v>
       </c>
       <c r="O168" t="n">
-        <v>0.9912490055688147</v>
+        <v>0.9912490055688148</v>
       </c>
       <c r="P168" t="n">
         <v>0.7528492820416096</v>
@@ -9556,7 +9556,7 @@
         <v>87625439</v>
       </c>
       <c r="J169" t="n">
-        <v>0.02861569516841573</v>
+        <v>0.0286156951684157</v>
       </c>
       <c r="K169" t="n">
         <v>12.6</v>
@@ -9571,7 +9571,7 @@
         <v>12.24</v>
       </c>
       <c r="O169" t="n">
-        <v>0.9910130718954249</v>
+        <v>0.9910130718954248</v>
       </c>
       <c r="P169" t="n">
         <v>0.8624460745427363</v>
@@ -9610,7 +9610,7 @@
         <v>71168943</v>
       </c>
       <c r="J170" t="n">
-        <v>0.02378811393525486</v>
+        <v>0.0237881139352548</v>
       </c>
       <c r="K170" t="n">
         <v>12.26</v>
@@ -9625,7 +9625,7 @@
         <v>12.29</v>
       </c>
       <c r="O170" t="n">
-        <v>0.9910496338486575</v>
+        <v>0.9910496338486576</v>
       </c>
       <c r="P170" t="n">
         <v>0.7193778683049603</v>
@@ -9733,7 +9733,7 @@
         <v>12</v>
       </c>
       <c r="O172" t="n">
-        <v>0.9908333333333333</v>
+        <v>0.9908333333333332</v>
       </c>
       <c r="P172" t="n">
         <v>1.277712039993257</v>
@@ -9772,7 +9772,7 @@
         <v>91485845</v>
       </c>
       <c r="J173" t="n">
-        <v>0.03174425644724667</v>
+        <v>0.0317442564472466</v>
       </c>
       <c r="K173" t="n">
         <v>12</v>
@@ -9826,7 +9826,7 @@
         <v>81649155</v>
       </c>
       <c r="J174" t="n">
-        <v>0.02836089313567279</v>
+        <v>0.0283608931356727</v>
       </c>
       <c r="K174" t="n">
         <v>11.76</v>
@@ -9880,7 +9880,7 @@
         <v>87948823</v>
       </c>
       <c r="J175" t="n">
-        <v>0.03061814969066606</v>
+        <v>0.030618149690666</v>
       </c>
       <c r="K175" t="n">
         <v>11.83</v>
@@ -9898,7 +9898,7 @@
         <v>0.9914965986394558</v>
       </c>
       <c r="P175" t="n">
-        <v>0.9649422645482513</v>
+        <v>0.9649422645482512</v>
       </c>
     </row>
     <row r="176">
@@ -9934,7 +9934,7 @@
         <v>80180111</v>
       </c>
       <c r="J176" t="n">
-        <v>0.02738136073882349</v>
+        <v>0.0273813607388234</v>
       </c>
       <c r="K176" t="n">
         <v>11.7</v>
@@ -9988,7 +9988,7 @@
         <v>77960881</v>
       </c>
       <c r="J177" t="n">
-        <v>0.02685613425110607</v>
+        <v>0.026856134251106</v>
       </c>
       <c r="K177" t="n">
         <v>12.04</v>
@@ -10042,7 +10042,7 @@
         <v>71552006</v>
       </c>
       <c r="J178" t="n">
-        <v>0.02513571092602573</v>
+        <v>0.0251357109260257</v>
       </c>
       <c r="K178" t="n">
         <v>11.87</v>
@@ -10057,7 +10057,7 @@
         <v>11.61</v>
       </c>
       <c r="O178" t="n">
-        <v>0.9913867355727821</v>
+        <v>0.991386735572782</v>
       </c>
       <c r="P178" t="n">
         <v>0.8669830713100642</v>
@@ -10096,7 +10096,7 @@
         <v>54677000</v>
       </c>
       <c r="J179" t="n">
-        <v>0.01929890980157661</v>
+        <v>0.0192989098015766</v>
       </c>
       <c r="K179" t="n">
         <v>11.59</v>
@@ -10150,7 +10150,7 @@
         <v>64218573</v>
       </c>
       <c r="J180" t="n">
-        <v>0.02272561391971193</v>
+        <v>0.0227256139197119</v>
       </c>
       <c r="K180" t="n">
         <v>11.55</v>
@@ -10165,7 +10165,7 @@
         <v>11.45</v>
       </c>
       <c r="O180" t="n">
-        <v>0.9912663755458515</v>
+        <v>0.9912663755458516</v>
       </c>
       <c r="P180" t="n">
         <v>0.8788602083831348</v>
@@ -10204,7 +10204,7 @@
         <v>77440898</v>
       </c>
       <c r="J181" t="n">
-        <v>0.02821290411505569</v>
+        <v>0.0282129041150556</v>
       </c>
       <c r="K181" t="n">
         <v>11.31</v>
@@ -10222,7 +10222,7 @@
         <v>0.9910233393177736</v>
       </c>
       <c r="P181" t="n">
-        <v>1.162002955053626</v>
+        <v>1.162002955053625</v>
       </c>
     </row>
     <row r="182">
@@ -10258,7 +10258,7 @@
         <v>57296422</v>
       </c>
       <c r="J182" t="n">
-        <v>0.02098447620857772</v>
+        <v>0.0209844762085777</v>
       </c>
       <c r="K182" t="n">
         <v>11.21</v>
@@ -10312,7 +10312,7 @@
         <v>70073806</v>
       </c>
       <c r="J183" t="n">
-        <v>0.02598344340421028</v>
+        <v>0.0259834434042102</v>
       </c>
       <c r="K183" t="n">
         <v>11.09</v>
@@ -10366,7 +10366,7 @@
         <v>59922455</v>
       </c>
       <c r="J184" t="n">
-        <v>0.02251451960845758</v>
+        <v>0.0225145196084575</v>
       </c>
       <c r="K184" t="n">
         <v>10.88</v>
@@ -10384,7 +10384,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="n">
-        <v>0.9604732249195801</v>
+        <v>0.96047322491958</v>
       </c>
     </row>
     <row r="185">
@@ -10420,7 +10420,7 @@
         <v>64197119</v>
       </c>
       <c r="J185" t="n">
-        <v>0.02396525230841775</v>
+        <v>0.0239652523084177</v>
       </c>
       <c r="K185" t="n">
         <v>10.9</v>
@@ -10474,7 +10474,7 @@
         <v>64289602</v>
       </c>
       <c r="J186" t="n">
-        <v>0.02399868233511362</v>
+        <v>0.0239986823351136</v>
       </c>
       <c r="K186" t="n">
         <v>10.96</v>
@@ -10492,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="n">
-        <v>0.9862964342701435</v>
+        <v>0.9862964342701436</v>
       </c>
     </row>
     <row r="187">
@@ -10528,7 +10528,7 @@
         <v>80742490</v>
       </c>
       <c r="J187" t="n">
-        <v>0.03027436671125676</v>
+        <v>0.0302743667112567</v>
       </c>
       <c r="K187" t="n">
         <v>10.79</v>
@@ -10582,7 +10582,7 @@
         <v>90092878</v>
       </c>
       <c r="J188" t="n">
-        <v>0.03413632570013983</v>
+        <v>0.0341363257001398</v>
       </c>
       <c r="K188" t="n">
         <v>10.94</v>
@@ -10636,7 +10636,7 @@
         <v>64403382</v>
       </c>
       <c r="J189" t="n">
-        <v>0.02443123018906551</v>
+        <v>0.0244312301890655</v>
       </c>
       <c r="K189" t="n">
         <v>10.73</v>
@@ -10654,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="n">
-        <v>0.9056040012631037</v>
+        <v>0.9056040012631036</v>
       </c>
     </row>
     <row r="190">
@@ -10690,7 +10690,7 @@
         <v>191605327</v>
       </c>
       <c r="J190" t="n">
-        <v>0.07045484531484313</v>
+        <v>0.0704548453148431</v>
       </c>
       <c r="K190" t="n">
         <v>10.78</v>
@@ -10744,7 +10744,7 @@
         <v>236953552</v>
       </c>
       <c r="J191" t="n">
-        <v>0.08519727916926483</v>
+        <v>0.0851972791692648</v>
       </c>
       <c r="K191" t="n">
         <v>11.12</v>
@@ -10798,7 +10798,7 @@
         <v>174281177</v>
       </c>
       <c r="J192" t="n">
-        <v>0.06348747737903226</v>
+        <v>0.0634874773790322</v>
       </c>
       <c r="K192" t="n">
         <v>11.33</v>
@@ -10852,7 +10852,7 @@
         <v>141408406</v>
       </c>
       <c r="J193" t="n">
-        <v>0.05449909717932234</v>
+        <v>0.0544990971793223</v>
       </c>
       <c r="K193" t="n">
         <v>10.97</v>
@@ -10870,7 +10870,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="n">
-        <v>0.9812332101991353</v>
+        <v>0.9812332101991352</v>
       </c>
     </row>
     <row r="194">
@@ -10906,7 +10906,7 @@
         <v>89993659</v>
       </c>
       <c r="J194" t="n">
-        <v>0.03572874871446769</v>
+        <v>0.0357287487144676</v>
       </c>
       <c r="K194" t="n">
         <v>10.49</v>
@@ -11014,7 +11014,7 @@
         <v>104022359</v>
       </c>
       <c r="J196" t="n">
-        <v>0.04140290795894968</v>
+        <v>0.0414029079589496</v>
       </c>
       <c r="K196" t="n">
         <v>10.45</v>
@@ -11068,7 +11068,7 @@
         <v>123748595</v>
       </c>
       <c r="J197" t="n">
-        <v>0.04838798299485519</v>
+        <v>0.0483879829948551</v>
       </c>
       <c r="K197" t="n">
         <v>10.1</v>
@@ -11122,7 +11122,7 @@
         <v>126693132</v>
       </c>
       <c r="J198" t="n">
-        <v>0.04756491322122094</v>
+        <v>0.0475649132212209</v>
       </c>
       <c r="K198" t="n">
         <v>10.66</v>
@@ -11230,7 +11230,7 @@
         <v>121733505</v>
       </c>
       <c r="J200" t="n">
-        <v>0.04498425743342459</v>
+        <v>0.0449842574334245</v>
       </c>
       <c r="K200" t="n">
         <v>10.81</v>
@@ -11284,7 +11284,7 @@
         <v>82348071</v>
       </c>
       <c r="J201" t="n">
-        <v>0.03146319070282113</v>
+        <v>0.0314631907028211</v>
       </c>
       <c r="K201" t="n">
         <v>10.82</v>
@@ -11338,7 +11338,7 @@
         <v>76225568</v>
       </c>
       <c r="J202" t="n">
-        <v>0.02971003388781085</v>
+        <v>0.0297100338878108</v>
       </c>
       <c r="K202" t="n">
         <v>10.49</v>
@@ -11392,7 +11392,7 @@
         <v>83925137</v>
       </c>
       <c r="J203" t="n">
-        <v>0.03371035791955321</v>
+        <v>0.0337103579195532</v>
       </c>
       <c r="K203" t="n">
         <v>10.31</v>
@@ -11446,7 +11446,7 @@
         <v>136955546</v>
       </c>
       <c r="J204" t="n">
-        <v>0.0535613120299113</v>
+        <v>0.0535613120299112</v>
       </c>
       <c r="K204" t="n">
         <v>10.07</v>
@@ -11500,7 +11500,7 @@
         <v>87829432</v>
       </c>
       <c r="J205" t="n">
-        <v>0.03447508683560959</v>
+        <v>0.0344750868356095</v>
       </c>
       <c r="K205" t="n">
         <v>10.5</v>
@@ -11554,7 +11554,7 @@
         <v>175959161</v>
       </c>
       <c r="J206" t="n">
-        <v>0.06691235532064733</v>
+        <v>0.06691235532064729</v>
       </c>
       <c r="K206" t="n">
         <v>10.29</v>
@@ -11608,7 +11608,7 @@
         <v>284314064</v>
       </c>
       <c r="J207" t="n">
-        <v>0.09934399774573303</v>
+        <v>0.09934399774573301</v>
       </c>
       <c r="K207" t="n">
         <v>11.22</v>
@@ -11932,7 +11932,7 @@
         <v>286426812</v>
       </c>
       <c r="J213" t="n">
-        <v>0.09539346963680782</v>
+        <v>0.0953934696368078</v>
       </c>
       <c r="K213" t="n">
         <v>12.07</v>
@@ -11986,7 +11986,7 @@
         <v>246469411</v>
       </c>
       <c r="J214" t="n">
-        <v>0.08396711285433751</v>
+        <v>0.0839671128543375</v>
       </c>
       <c r="K214" t="n">
         <v>12.18</v>
@@ -12004,7 +12004,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="n">
-        <v>0.4869817663471973</v>
+        <v>0.4869817663471972</v>
       </c>
     </row>
     <row r="215">
@@ -12040,7 +12040,7 @@
         <v>145700950</v>
       </c>
       <c r="J215" t="n">
-        <v>0.04718582995300559</v>
+        <v>0.0471858299530055</v>
       </c>
       <c r="K215" t="n">
         <v>11.94</v>
@@ -12094,7 +12094,7 @@
         <v>560368375</v>
       </c>
       <c r="J216" t="n">
-        <v>0.1727265866233032</v>
+        <v>0.1727265866233031</v>
       </c>
       <c r="K216" t="n">
         <v>13.16</v>
@@ -12256,7 +12256,7 @@
         <v>226555906</v>
       </c>
       <c r="J219" t="n">
-        <v>0.07401786956326846</v>
+        <v>0.0740178695632684</v>
       </c>
       <c r="K219" t="n">
         <v>12.18</v>
@@ -12310,7 +12310,7 @@
         <v>170775210</v>
       </c>
       <c r="J220" t="n">
-        <v>0.05557057263043718</v>
+        <v>0.0555705726304371</v>
       </c>
       <c r="K220" t="n">
         <v>12.42</v>
@@ -12364,7 +12364,7 @@
         <v>287239574</v>
       </c>
       <c r="J221" t="n">
-        <v>0.09149756560345165</v>
+        <v>0.0914975656034516</v>
       </c>
       <c r="K221" t="n">
         <v>12.73</v>
@@ -12418,7 +12418,7 @@
         <v>248827502</v>
       </c>
       <c r="J222" t="n">
-        <v>0.07997879814014834</v>
+        <v>0.0799787981401483</v>
       </c>
       <c r="K222" t="n">
         <v>12.69</v>
@@ -12472,7 +12472,7 @@
         <v>358573912</v>
       </c>
       <c r="J223" t="n">
-        <v>0.1140199455875327</v>
+        <v>0.1140199455875326</v>
       </c>
       <c r="K223" t="n">
         <v>12.97</v>
@@ -12634,7 +12634,7 @@
         <v>372583228</v>
       </c>
       <c r="J226" t="n">
-        <v>0.1113355333670319</v>
+        <v>0.1113355333670318</v>
       </c>
       <c r="K226" t="n">
         <v>13.52</v>
@@ -12688,7 +12688,7 @@
         <v>248782419</v>
       </c>
       <c r="J227" t="n">
-        <v>0.07515817665519671</v>
+        <v>0.0751581766551967</v>
       </c>
       <c r="K227" t="n">
         <v>13.4</v>
@@ -12796,7 +12796,7 @@
         <v>223186371</v>
       </c>
       <c r="J229" t="n">
-        <v>0.06883435499854522</v>
+        <v>0.06883435499854521</v>
       </c>
       <c r="K229" t="n">
         <v>13.4</v>
@@ -12904,7 +12904,7 @@
         <v>340236879</v>
       </c>
       <c r="J231" t="n">
-        <v>0.09027037618771998</v>
+        <v>0.09027037618771989</v>
       </c>
       <c r="K231" t="n">
         <v>14.5</v>
@@ -13498,7 +13498,7 @@
         <v>67229630</v>
       </c>
       <c r="J242" t="n">
-        <v>0.01035661109197304</v>
+        <v>0.010356611091973</v>
       </c>
       <c r="K242" t="n">
         <v>4.04</v>
@@ -13552,7 +13552,7 @@
         <v>77015600</v>
       </c>
       <c r="J243" t="n">
-        <v>0.01173961339954121</v>
+        <v>0.0117396133995412</v>
       </c>
       <c r="K243" t="n">
         <v>4.06</v>
@@ -13567,7 +13567,7 @@
         <v>4.08</v>
       </c>
       <c r="O243" t="n">
-        <v>0.9607843137254901</v>
+        <v>0.96078431372549</v>
       </c>
       <c r="P243" t="n">
         <v>1.286505284616421</v>
@@ -13606,7 +13606,7 @@
         <v>82809554</v>
       </c>
       <c r="J244" t="n">
-        <v>0.01262237648114282</v>
+        <v>0.0126223764811428</v>
       </c>
       <c r="K244" t="n">
         <v>4.08</v>
@@ -13660,7 +13660,7 @@
         <v>57134469</v>
       </c>
       <c r="J245" t="n">
-        <v>0.008743282246710211</v>
+        <v>0.008743282246710201</v>
       </c>
       <c r="K245" t="n">
         <v>4.06</v>
@@ -13714,7 +13714,7 @@
         <v>60394095</v>
       </c>
       <c r="J246" t="n">
-        <v>0.009215509860257173</v>
+        <v>0.0092155098602571</v>
       </c>
       <c r="K246" t="n">
         <v>4.06</v>
@@ -13768,7 +13768,7 @@
         <v>68550614</v>
       </c>
       <c r="J247" t="n">
-        <v>0.01061012646608399</v>
+        <v>0.0106101264660839</v>
       </c>
       <c r="K247" t="n">
         <v>4.05</v>
@@ -13822,7 +13822,7 @@
         <v>49741940</v>
       </c>
       <c r="J248" t="n">
-        <v>0.007722791417681304</v>
+        <v>0.0077227914176813</v>
       </c>
       <c r="K248" t="n">
         <v>3.99</v>
@@ -13876,7 +13876,7 @@
         <v>76592120</v>
       </c>
       <c r="J249" t="n">
-        <v>0.01202111553600861</v>
+        <v>0.0120211155360086</v>
       </c>
       <c r="K249" t="n">
         <v>4</v>
@@ -13891,7 +13891,7 @@
         <v>3.93</v>
       </c>
       <c r="O249" t="n">
-        <v>0.9592875318066157</v>
+        <v>0.9592875318066156</v>
       </c>
       <c r="P249" t="n">
         <v>1.228798941478799</v>
@@ -13930,7 +13930,7 @@
         <v>101825314</v>
       </c>
       <c r="J250" t="n">
-        <v>0.0165431517264751</v>
+        <v>0.016543151726475</v>
       </c>
       <c r="K250" t="n">
         <v>3.92</v>
@@ -13984,7 +13984,7 @@
         <v>49565369</v>
       </c>
       <c r="J251" t="n">
-        <v>0.008109767783378928</v>
+        <v>0.0081097677833789</v>
       </c>
       <c r="K251" t="n">
         <v>3.81</v>
@@ -14038,7 +14038,7 @@
         <v>73415758</v>
       </c>
       <c r="J252" t="n">
-        <v>0.01173382084982398</v>
+        <v>0.0117338208498239</v>
       </c>
       <c r="K252" t="n">
         <v>3.83</v>
@@ -14053,7 +14053,7 @@
         <v>3.93</v>
       </c>
       <c r="O252" t="n">
-        <v>0.9592875318066157</v>
+        <v>0.9592875318066156</v>
       </c>
       <c r="P252" t="n">
         <v>1.066576153094265</v>
@@ -14092,7 +14092,7 @@
         <v>63382621</v>
       </c>
       <c r="J253" t="n">
-        <v>0.009993109338417775</v>
+        <v>0.0099931093384177</v>
       </c>
       <c r="K253" t="n">
         <v>3.92</v>
@@ -14107,7 +14107,7 @@
         <v>3.93</v>
       </c>
       <c r="O253" t="n">
-        <v>0.9592875318066157</v>
+        <v>0.9592875318066156</v>
       </c>
       <c r="P253" t="n">
         <v>0.8901651608102731</v>
@@ -14146,7 +14146,7 @@
         <v>49166087</v>
       </c>
       <c r="J254" t="n">
-        <v>0.007824031196152981</v>
+        <v>0.0078240311961529</v>
       </c>
       <c r="K254" t="n">
         <v>3.91</v>
@@ -14161,7 +14161,7 @@
         <v>3.92</v>
       </c>
       <c r="O254" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="P254" t="n">
         <v>0.6698546132576576</v>
@@ -14200,7 +14200,7 @@
         <v>26094343</v>
       </c>
       <c r="J255" t="n">
-        <v>0.004166316234182566</v>
+        <v>0.0041663162341825</v>
       </c>
       <c r="K255" t="n">
         <v>3.89</v>
@@ -14215,10 +14215,10 @@
         <v>3.92</v>
       </c>
       <c r="O255" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="P255" t="n">
-        <v>0.3843189975927194</v>
+        <v>0.3843189975927193</v>
       </c>
     </row>
     <row r="256">
@@ -14254,7 +14254,7 @@
         <v>37487508</v>
       </c>
       <c r="J256" t="n">
-        <v>0.005915596668609979</v>
+        <v>0.0059155966686099</v>
       </c>
       <c r="K256" t="n">
         <v>3.92</v>
@@ -14269,7 +14269,7 @@
         <v>3.92</v>
       </c>
       <c r="O256" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="P256" t="n">
         <v>0.7071497175764309</v>
@@ -14308,7 +14308,7 @@
         <v>32658942</v>
       </c>
       <c r="J257" t="n">
-        <v>0.005184171714015797</v>
+        <v>0.0051841717140157</v>
       </c>
       <c r="K257" t="n">
         <v>3.94</v>
@@ -14323,7 +14323,7 @@
         <v>3.92</v>
       </c>
       <c r="O257" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="P257" t="n">
         <v>0.65402419169126</v>
@@ -14362,7 +14362,7 @@
         <v>33313554</v>
       </c>
       <c r="J258" t="n">
-        <v>0.005324649742180781</v>
+        <v>0.0053246497421807</v>
       </c>
       <c r="K258" t="n">
         <v>3.91</v>
@@ -14416,7 +14416,7 @@
         <v>40138916</v>
       </c>
       <c r="J259" t="n">
-        <v>0.006533892953276169</v>
+        <v>0.0065338929532761</v>
       </c>
       <c r="K259" t="n">
         <v>3.88</v>
@@ -14431,7 +14431,7 @@
         <v>3.8</v>
       </c>
       <c r="O259" t="n">
-        <v>0.9605263157894737</v>
+        <v>0.9605263157894736</v>
       </c>
       <c r="P259" t="n">
         <v>1.149735502937091</v>
@@ -14470,7 +14470,7 @@
         <v>24296070</v>
       </c>
       <c r="J260" t="n">
-        <v>0.003971443281565446</v>
+        <v>0.0039714432815654</v>
       </c>
       <c r="K260" t="n">
         <v>3.79</v>
@@ -14524,7 +14524,7 @@
         <v>68516183</v>
       </c>
       <c r="J261" t="n">
-        <v>0.01093607728923295</v>
+        <v>0.0109360772892329</v>
       </c>
       <c r="K261" t="n">
         <v>3.85</v>
@@ -14578,7 +14578,7 @@
         <v>46268188</v>
       </c>
       <c r="J262" t="n">
-        <v>0.007474045391937923</v>
+        <v>0.0074740453919379</v>
       </c>
       <c r="K262" t="n">
         <v>3.88</v>
@@ -14632,7 +14632,7 @@
         <v>32879590</v>
       </c>
       <c r="J263" t="n">
-        <v>0.005296668571088531</v>
+        <v>0.0052966685710885</v>
       </c>
       <c r="K263" t="n">
         <v>3.86</v>
@@ -14686,7 +14686,7 @@
         <v>22987524</v>
       </c>
       <c r="J264" t="n">
-        <v>0.00372679689498809</v>
+        <v>0.003726796894988</v>
       </c>
       <c r="K264" t="n">
         <v>3.84</v>
@@ -14740,7 +14740,7 @@
         <v>23616427</v>
       </c>
       <c r="J265" t="n">
-        <v>0.003816198724632883</v>
+        <v>0.0038161987246328</v>
       </c>
       <c r="K265" t="n">
         <v>3.85</v>
@@ -14794,7 +14794,7 @@
         <v>31019821</v>
       </c>
       <c r="J266" t="n">
-        <v>0.004985259383635758</v>
+        <v>0.0049852593836357</v>
       </c>
       <c r="K266" t="n">
         <v>3.87</v>
@@ -14848,7 +14848,7 @@
         <v>26443065</v>
       </c>
       <c r="J267" t="n">
-        <v>0.004249164480926557</v>
+        <v>0.0042491644809265</v>
       </c>
       <c r="K267" t="n">
         <v>3.87</v>
@@ -14902,7 +14902,7 @@
         <v>54265493</v>
       </c>
       <c r="J268" t="n">
-        <v>0.008648139431229196</v>
+        <v>0.0086481394312291</v>
       </c>
       <c r="K268" t="n">
         <v>3.88</v>
@@ -14956,7 +14956,7 @@
         <v>45783700</v>
       </c>
       <c r="J269" t="n">
-        <v>0.007379192079692453</v>
+        <v>0.0073791920796924</v>
       </c>
       <c r="K269" t="n">
         <v>3.86</v>
@@ -15010,7 +15010,7 @@
         <v>28316099</v>
       </c>
       <c r="J270" t="n">
-        <v>0.004554791058687352</v>
+        <v>0.0045547910586873</v>
       </c>
       <c r="K270" t="n">
         <v>3.85</v>
@@ -15064,7 +15064,7 @@
         <v>18028849</v>
       </c>
       <c r="J271" t="n">
-        <v>0.002902230176246998</v>
+        <v>0.0029022301762469</v>
       </c>
       <c r="K271" t="n">
         <v>3.86</v>
@@ -15082,7 +15082,7 @@
         <v>0.961139896373057</v>
       </c>
       <c r="P271" t="n">
-        <v>0.4866811424077087</v>
+        <v>0.4866811424077086</v>
       </c>
     </row>
     <row r="272">
@@ -15118,7 +15118,7 @@
         <v>55403077</v>
       </c>
       <c r="J272" t="n">
-        <v>0.008995266856931921</v>
+        <v>0.0089952668569319</v>
       </c>
       <c r="K272" t="n">
         <v>3.86</v>
@@ -15172,7 +15172,7 @@
         <v>40114443</v>
       </c>
       <c r="J273" t="n">
-        <v>0.006548176769567312</v>
+        <v>0.0065481767695673</v>
       </c>
       <c r="K273" t="n">
         <v>3.82</v>
@@ -15187,7 +15187,7 @@
         <v>3.8</v>
       </c>
       <c r="O273" t="n">
-        <v>0.9605263157894737</v>
+        <v>0.9605263157894736</v>
       </c>
       <c r="P273" t="n">
         <v>1.00804394411769</v>
@@ -15226,7 +15226,7 @@
         <v>43827491</v>
       </c>
       <c r="J274" t="n">
-        <v>0.007089385673376245</v>
+        <v>0.0070893856733762</v>
       </c>
       <c r="K274" t="n">
         <v>3.82</v>
@@ -15280,7 +15280,7 @@
         <v>35152305</v>
       </c>
       <c r="J275" t="n">
-        <v>0.005656363916222788</v>
+        <v>0.0056563639162227</v>
       </c>
       <c r="K275" t="n">
         <v>3.85</v>
@@ -15298,7 +15298,7 @@
         <v>0.961340206185567</v>
       </c>
       <c r="P275" t="n">
-        <v>0.9399122653798415</v>
+        <v>0.9399122653798416</v>
       </c>
     </row>
     <row r="276">
@@ -15334,7 +15334,7 @@
         <v>32784497</v>
       </c>
       <c r="J276" t="n">
-        <v>0.005232165883455423</v>
+        <v>0.0052321658834554</v>
       </c>
       <c r="K276" t="n">
         <v>3.88</v>
@@ -15388,7 +15388,7 @@
         <v>32313173</v>
       </c>
       <c r="J277" t="n">
-        <v>0.005170041346864526</v>
+        <v>0.0051700413468645</v>
       </c>
       <c r="K277" t="n">
         <v>3.9</v>
@@ -15403,7 +15403,7 @@
         <v>3.89</v>
       </c>
       <c r="O277" t="n">
-        <v>0.9614395886889461</v>
+        <v>0.961439588688946</v>
       </c>
       <c r="P277" t="n">
         <v>0.7711562844916633</v>
@@ -15442,7 +15442,7 @@
         <v>32314259</v>
       </c>
       <c r="J278" t="n">
-        <v>0.005164022661572747</v>
+        <v>0.0051640226615727</v>
       </c>
       <c r="K278" t="n">
         <v>3.9</v>
@@ -15496,7 +15496,7 @@
         <v>27134218</v>
       </c>
       <c r="J279" t="n">
-        <v>0.004335053754146937</v>
+        <v>0.0043350537541469</v>
       </c>
       <c r="K279" t="n">
         <v>3.89</v>
@@ -15511,7 +15511,7 @@
         <v>3.89</v>
       </c>
       <c r="O279" t="n">
-        <v>0.9614395886889461</v>
+        <v>0.961439588688946</v>
       </c>
       <c r="P279" t="n">
         <v>0.7655864820368482</v>
@@ -15550,7 +15550,7 @@
         <v>287783817</v>
       </c>
       <c r="J280" t="n">
-        <v>0.04413500122831998</v>
+        <v>0.0441350012283199</v>
       </c>
       <c r="K280" t="n">
         <v>3.88</v>
@@ -15565,7 +15565,7 @@
         <v>4.11</v>
       </c>
       <c r="O280" t="n">
-        <v>0.9610705596107055</v>
+        <v>0.9610705596107056</v>
       </c>
       <c r="P280" t="n">
         <v>8.634402114044383</v>
@@ -15604,7 +15604,7 @@
         <v>122121393</v>
       </c>
       <c r="J281" t="n">
-        <v>0.01887287434439212</v>
+        <v>0.0188728743443921</v>
       </c>
       <c r="K281" t="n">
         <v>4.07</v>
@@ -15658,7 +15658,7 @@
         <v>74360671</v>
       </c>
       <c r="J282" t="n">
-        <v>0.01157641433739849</v>
+        <v>0.0115764143373984</v>
       </c>
       <c r="K282" t="n">
         <v>4.01</v>
@@ -15712,7 +15712,7 @@
         <v>52490535</v>
       </c>
       <c r="J283" t="n">
-        <v>0.008210621764620403</v>
+        <v>0.0082106217646204</v>
       </c>
       <c r="K283" t="n">
         <v>3.95</v>
@@ -15727,7 +15727,7 @@
         <v>3.98</v>
       </c>
       <c r="O283" t="n">
-        <v>0.9597989949748743</v>
+        <v>0.9597989949748744</v>
       </c>
       <c r="P283" t="n">
         <v>0.4882429262408178</v>
@@ -15766,7 +15766,7 @@
         <v>69080370</v>
       </c>
       <c r="J284" t="n">
-        <v>0.01088368279486334</v>
+        <v>0.0108836827948633</v>
       </c>
       <c r="K284" t="n">
         <v>3.97</v>
@@ -15820,7 +15820,7 @@
         <v>70727323</v>
       </c>
       <c r="J285" t="n">
-        <v>0.01129333360067031</v>
+        <v>0.0112933336006703</v>
       </c>
       <c r="K285" t="n">
         <v>3.91</v>
@@ -15874,7 +15874,7 @@
         <v>38395428</v>
       </c>
       <c r="J286" t="n">
-        <v>0.006133877759450566</v>
+        <v>0.0061338777594505</v>
       </c>
       <c r="K286" t="n">
         <v>3.88</v>
@@ -15928,7 +15928,7 @@
         <v>51601029</v>
       </c>
       <c r="J287" t="n">
-        <v>0.008130615743847706</v>
+        <v>0.008130615743847699</v>
       </c>
       <c r="K287" t="n">
         <v>3.9</v>
@@ -15982,7 +15982,7 @@
         <v>37697899</v>
       </c>
       <c r="J288" t="n">
-        <v>0.005973366231636119</v>
+        <v>0.0059733662316361</v>
       </c>
       <c r="K288" t="n">
         <v>3.96</v>
@@ -16036,7 +16036,7 @@
         <v>72347753</v>
       </c>
       <c r="J289" t="n">
-        <v>0.01138338836572403</v>
+        <v>0.011383388365724</v>
       </c>
       <c r="K289" t="n">
         <v>3.92</v>
@@ -16051,7 +16051,7 @@
         <v>3.92</v>
       </c>
       <c r="O289" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="P289" t="n">
         <v>1.341909891556533</v>
@@ -16090,7 +16090,7 @@
         <v>50304564</v>
       </c>
       <c r="J290" t="n">
-        <v>0.007976283184232271</v>
+        <v>0.0079762831842322</v>
       </c>
       <c r="K290" t="n">
         <v>3.95</v>
@@ -16108,7 +16108,7 @@
         <v>0.959079283887468</v>
       </c>
       <c r="P290" t="n">
-        <v>0.9293208587869455</v>
+        <v>0.9293208587869456</v>
       </c>
     </row>
     <row r="291">
@@ -16144,7 +16144,7 @@
         <v>50149210</v>
       </c>
       <c r="J291" t="n">
-        <v>0.007919687786689354</v>
+        <v>0.0079196877866893</v>
       </c>
       <c r="K291" t="n">
         <v>3.91</v>
@@ -16213,7 +16213,7 @@
         <v>3.92</v>
       </c>
       <c r="O292" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="P292" t="n">
         <v>0.6982855636498391</v>
@@ -16252,7 +16252,7 @@
         <v>49854791</v>
       </c>
       <c r="J293" t="n">
-        <v>0.007870452977847614</v>
+        <v>0.0078704529778476</v>
       </c>
       <c r="K293" t="n">
         <v>3.92</v>
@@ -16267,7 +16267,7 @@
         <v>3.93</v>
       </c>
       <c r="O293" t="n">
-        <v>0.9592875318066157</v>
+        <v>0.9592875318066156</v>
       </c>
       <c r="P293" t="n">
         <v>1.008199930550446</v>
@@ -16306,7 +16306,7 @@
         <v>59600872</v>
       </c>
       <c r="J294" t="n">
-        <v>0.009472938498060619</v>
+        <v>0.0094729384980606</v>
       </c>
       <c r="K294" t="n">
         <v>3.93</v>
@@ -16360,7 +16360,7 @@
         <v>65411600</v>
       </c>
       <c r="J295" t="n">
-        <v>0.01040554086628978</v>
+        <v>0.0104055408662897</v>
       </c>
       <c r="K295" t="n">
         <v>3.88</v>
@@ -16375,7 +16375,7 @@
         <v>3.92</v>
       </c>
       <c r="O295" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9591836734693876</v>
       </c>
       <c r="P295" t="n">
         <v>1.333399552249312</v>
@@ -16414,7 +16414,7 @@
         <v>76820371</v>
       </c>
       <c r="J296" t="n">
-        <v>0.01207514081577159</v>
+        <v>0.0120751408157715</v>
       </c>
       <c r="K296" t="n">
         <v>3.92</v>
@@ -16468,7 +16468,7 @@
         <v>66542968</v>
       </c>
       <c r="J297" t="n">
-        <v>0.01036959711371685</v>
+        <v>0.0103695971137168</v>
       </c>
       <c r="K297" t="n">
         <v>3.98</v>
@@ -16522,7 +16522,7 @@
         <v>151026472</v>
       </c>
       <c r="J298" t="n">
-        <v>0.02329674284544224</v>
+        <v>0.0232967428454422</v>
       </c>
       <c r="K298" t="n">
         <v>3.99</v>
@@ -16537,7 +16537,7 @@
         <v>4.05</v>
       </c>
       <c r="O298" t="n">
-        <v>0.9604938271604939</v>
+        <v>0.960493827160494</v>
       </c>
       <c r="P298" t="n">
         <v>2.320685329379431</v>
@@ -16576,7 +16576,7 @@
         <v>105490593</v>
       </c>
       <c r="J299" t="n">
-        <v>0.01636566512053177</v>
+        <v>0.0163656651205317</v>
       </c>
       <c r="K299" t="n">
         <v>4.02</v>
@@ -16591,7 +16591,7 @@
         <v>3.97</v>
       </c>
       <c r="O299" t="n">
-        <v>0.9596977329974811</v>
+        <v>0.9596977329974812</v>
       </c>
       <c r="P299" t="n">
         <v>1.247003585935969</v>
@@ -16738,7 +16738,7 @@
         <v>29104402</v>
       </c>
       <c r="J302" t="n">
-        <v>0.004702235802052791</v>
+        <v>0.0047022358020527</v>
       </c>
       <c r="K302" t="n">
         <v>3.86</v>
@@ -16756,7 +16756,7 @@
         <v>0.961139896373057</v>
       </c>
       <c r="P302" t="n">
-        <v>0.3210174403156221</v>
+        <v>0.321017440315622</v>
       </c>
     </row>
     <row r="303">
@@ -16792,7 +16792,7 @@
         <v>48165007</v>
       </c>
       <c r="J303" t="n">
-        <v>0.007844604563424095</v>
+        <v>0.007844604563424</v>
       </c>
       <c r="K303" t="n">
         <v>3.86</v>
@@ -16846,7 +16846,7 @@
         <v>48161340</v>
       </c>
       <c r="J304" t="n">
-        <v>0.007973299312901097</v>
+        <v>0.007973299312901</v>
       </c>
       <c r="K304" t="n">
         <v>3.8</v>
@@ -16900,7 +16900,7 @@
         <v>37521413</v>
       </c>
       <c r="J305" t="n">
-        <v>0.006193590597414019</v>
+        <v>0.006193590597414</v>
       </c>
       <c r="K305" t="n">
         <v>3.75</v>
@@ -16954,7 +16954,7 @@
         <v>40476327</v>
       </c>
       <c r="J306" t="n">
-        <v>0.006695495398862331</v>
+        <v>0.0066954953988623</v>
       </c>
       <c r="K306" t="n">
         <v>3.73</v>
@@ -17008,7 +17008,7 @@
         <v>30457721</v>
       </c>
       <c r="J307" t="n">
-        <v>0.005068284065828021</v>
+        <v>0.005068284065828</v>
       </c>
       <c r="K307" t="n">
         <v>3.75</v>
@@ -17062,7 +17062,7 @@
         <v>49572915</v>
       </c>
       <c r="J308" t="n">
-        <v>0.008379531371271997</v>
+        <v>0.008379531371271899</v>
       </c>
       <c r="K308" t="n">
         <v>3.72</v>
@@ -17077,7 +17077,7 @@
         <v>3.65</v>
       </c>
       <c r="O308" t="n">
-        <v>0.9616438356164383</v>
+        <v>0.9616438356164384</v>
       </c>
       <c r="P308" t="n">
         <v>1.240483110003403</v>
@@ -17116,7 +17116,7 @@
         <v>85785703</v>
       </c>
       <c r="J309" t="n">
-        <v>0.01510077826931161</v>
+        <v>0.0151007782693116</v>
       </c>
       <c r="K309" t="n">
         <v>3.65</v>
@@ -17170,7 +17170,7 @@
         <v>46428912</v>
       </c>
       <c r="J310" t="n">
-        <v>0.008351404206058816</v>
+        <v>0.0083514042060588</v>
       </c>
       <c r="K310" t="n">
         <v>3.49</v>
@@ -17224,7 +17224,7 @@
         <v>37686846</v>
       </c>
       <c r="J311" t="n">
-        <v>0.006571668155502287</v>
+        <v>0.0065716681555022</v>
       </c>
       <c r="K311" t="n">
         <v>3.53</v>
@@ -17278,7 +17278,7 @@
         <v>24716237</v>
       </c>
       <c r="J312" t="n">
-        <v>0.004342723726134169</v>
+        <v>0.0043427237261341</v>
       </c>
       <c r="K312" t="n">
         <v>3.53</v>
@@ -17296,7 +17296,7 @@
         <v>0.9606741573033708</v>
       </c>
       <c r="P312" t="n">
-        <v>0.4994889912137072</v>
+        <v>0.4994889912137071</v>
       </c>
     </row>
     <row r="313">
@@ -17332,7 +17332,7 @@
         <v>25791708</v>
       </c>
       <c r="J313" t="n">
-        <v>0.004557392860297794</v>
+        <v>0.0045573928602977</v>
       </c>
       <c r="K313" t="n">
         <v>3.55</v>
@@ -17386,7 +17386,7 @@
         <v>33061067</v>
       </c>
       <c r="J314" t="n">
-        <v>0.005871846268702572</v>
+        <v>0.0058718462687025</v>
       </c>
       <c r="K314" t="n">
         <v>3.49</v>
@@ -17401,7 +17401,7 @@
         <v>3.47</v>
       </c>
       <c r="O314" t="n">
-        <v>0.9596541786743515</v>
+        <v>0.9596541786743517</v>
       </c>
       <c r="P314" t="n">
         <v>0.7542712997266229</v>
@@ -17440,7 +17440,7 @@
         <v>38752051</v>
       </c>
       <c r="J315" t="n">
-        <v>0.006950257003639599</v>
+        <v>0.0069502570036395</v>
       </c>
       <c r="K315" t="n">
         <v>3.47</v>
@@ -17494,7 +17494,7 @@
         <v>27699488</v>
       </c>
       <c r="J316" t="n">
-        <v>0.005123822093184459</v>
+        <v>0.0051238220931844</v>
       </c>
       <c r="K316" t="n">
         <v>3.39</v>
@@ -17512,7 +17512,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="n">
-        <v>0.9054644753310505</v>
+        <v>0.9054644753310503</v>
       </c>
     </row>
     <row r="317">
@@ -17548,7 +17548,7 @@
         <v>28212362</v>
       </c>
       <c r="J317" t="n">
-        <v>0.005142960369309412</v>
+        <v>0.0051429603693094</v>
       </c>
       <c r="K317" t="n">
         <v>3.37</v>
@@ -17566,7 +17566,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="n">
-        <v>0.9578619407868055</v>
+        <v>0.9578619407868056</v>
       </c>
     </row>
     <row r="318">
@@ -17602,7 +17602,7 @@
         <v>27374233</v>
       </c>
       <c r="J318" t="n">
-        <v>0.004929429989289039</v>
+        <v>0.004929429989289</v>
       </c>
       <c r="K318" t="n">
         <v>3.41</v>
@@ -17656,7 +17656,7 @@
         <v>21344963</v>
       </c>
       <c r="J319" t="n">
-        <v>0.003815994332863581</v>
+        <v>0.0038159943328635</v>
       </c>
       <c r="K319" t="n">
         <v>3.46</v>
@@ -17710,7 +17710,7 @@
         <v>42341428</v>
       </c>
       <c r="J320" t="n">
-        <v>0.007434891632459281</v>
+        <v>0.0074348916324592</v>
       </c>
       <c r="K320" t="n">
         <v>3.52</v>
@@ -17764,7 +17764,7 @@
         <v>32326888</v>
       </c>
       <c r="J321" t="n">
-        <v>0.005711175700484048</v>
+        <v>0.005711175700484</v>
       </c>
       <c r="K321" t="n">
         <v>3.58</v>
@@ -17818,7 +17818,7 @@
         <v>27874182</v>
       </c>
       <c r="J322" t="n">
-        <v>0.004919548361682615</v>
+        <v>0.0049195483616826</v>
       </c>
       <c r="K322" t="n">
         <v>3.51</v>
@@ -17836,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="n">
-        <v>0.9098664839297447</v>
+        <v>0.9098664839297448</v>
       </c>
     </row>
     <row r="323">
@@ -17872,7 +17872,7 @@
         <v>24348341</v>
       </c>
       <c r="J323" t="n">
-        <v>0.004287623059888942</v>
+        <v>0.0042876230598889</v>
       </c>
       <c r="K323" t="n">
         <v>3.53</v>
@@ -17926,7 +17926,7 @@
         <v>42256081</v>
       </c>
       <c r="J324" t="n">
-        <v>0.007327707097633658</v>
+        <v>0.0073277070976336</v>
       </c>
       <c r="K324" t="n">
         <v>3.54</v>
@@ -17980,7 +17980,7 @@
         <v>74730715</v>
       </c>
       <c r="J325" t="n">
-        <v>0.01261964608045564</v>
+        <v>0.0126196460804556</v>
       </c>
       <c r="K325" t="n">
         <v>3.67</v>
@@ -18034,7 +18034,7 @@
         <v>95495395</v>
       </c>
       <c r="J326" t="n">
-        <v>0.01573859800608138</v>
+        <v>0.0157385980060813</v>
       </c>
       <c r="K326" t="n">
         <v>3.69</v>
@@ -18088,7 +18088,7 @@
         <v>68946065</v>
       </c>
       <c r="J327" t="n">
-        <v>0.01122540222557588</v>
+        <v>0.0112254022255758</v>
       </c>
       <c r="K327" t="n">
         <v>3.82</v>
@@ -18142,7 +18142,7 @@
         <v>67909729</v>
       </c>
       <c r="J328" t="n">
-        <v>0.01092984427214662</v>
+        <v>0.0109298442721466</v>
       </c>
       <c r="K328" t="n">
         <v>3.82</v>
@@ -18196,7 +18196,7 @@
         <v>112478291</v>
       </c>
       <c r="J329" t="n">
-        <v>0.01801076663526998</v>
+        <v>0.0180107666352699</v>
       </c>
       <c r="K329" t="n">
         <v>3.86</v>
@@ -18250,7 +18250,7 @@
         <v>86075733</v>
       </c>
       <c r="J330" t="n">
-        <v>0.01405771488543222</v>
+        <v>0.0140577148854322</v>
       </c>
       <c r="K330" t="n">
         <v>3.82</v>
@@ -18304,7 +18304,7 @@
         <v>82171287</v>
       </c>
       <c r="J331" t="n">
-        <v>0.01360811760313254</v>
+        <v>0.0136081176031325</v>
       </c>
       <c r="K331" t="n">
         <v>3.78</v>
@@ -18322,7 +18322,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="n">
-        <v>0.9725318165069261</v>
+        <v>0.972531816506926</v>
       </c>
     </row>
     <row r="332">
@@ -18358,7 +18358,7 @@
         <v>48536337</v>
       </c>
       <c r="J332" t="n">
-        <v>0.008144344782479315</v>
+        <v>0.0081443447824793</v>
       </c>
       <c r="K332" t="n">
         <v>3.7</v>
@@ -18412,7 +18412,7 @@
         <v>56521044</v>
       </c>
       <c r="J333" t="n">
-        <v>0.009313055676843537</v>
+        <v>0.0093130556768435</v>
       </c>
       <c r="K333" t="n">
         <v>3.72</v>
@@ -18466,7 +18466,7 @@
         <v>43841205</v>
       </c>
       <c r="J334" t="n">
-        <v>0.007189871873683292</v>
+        <v>0.0071898718736832</v>
       </c>
       <c r="K334" t="n">
         <v>3.78</v>
@@ -18520,7 +18520,7 @@
         <v>33823215</v>
       </c>
       <c r="J335" t="n">
-        <v>0.005562059790372645</v>
+        <v>0.0055620597903726</v>
       </c>
       <c r="K335" t="n">
         <v>3.73</v>
@@ -18574,7 +18574,7 @@
         <v>36673198</v>
       </c>
       <c r="J336" t="n">
-        <v>0.006008117802430043</v>
+        <v>0.00600811780243</v>
       </c>
       <c r="K336" t="n">
         <v>3.77</v>
@@ -18628,7 +18628,7 @@
         <v>48956785</v>
       </c>
       <c r="J337" t="n">
-        <v>0.007904718108655631</v>
+        <v>0.0079047181086556</v>
       </c>
       <c r="K337" t="n">
         <v>3.8</v>
@@ -18682,7 +18682,7 @@
         <v>51499663</v>
       </c>
       <c r="J338" t="n">
-        <v>0.008253002304797384</v>
+        <v>0.008253002304797301</v>
       </c>
       <c r="K338" t="n">
         <v>3.85</v>
@@ -18736,7 +18736,7 @@
         <v>48521583</v>
       </c>
       <c r="J339" t="n">
-        <v>0.007811177500995373</v>
+        <v>0.0078111775009953</v>
       </c>
       <c r="K339" t="n">
         <v>3.86</v>
@@ -18790,7 +18790,7 @@
         <v>120273053</v>
       </c>
       <c r="J340" t="n">
-        <v>0.01891437767734037</v>
+        <v>0.0189143776773403</v>
       </c>
       <c r="K340" t="n">
         <v>3.88</v>
@@ -18844,7 +18844,7 @@
         <v>98551722</v>
       </c>
       <c r="J341" t="n">
-        <v>0.01568473549423195</v>
+        <v>0.0156847354942319</v>
       </c>
       <c r="K341" t="n">
         <v>3.96</v>
@@ -18898,7 +18898,7 @@
         <v>76896290</v>
       </c>
       <c r="J342" t="n">
-        <v>0.01220378275886442</v>
+        <v>0.0122037827588644</v>
       </c>
       <c r="K342" t="n">
         <v>3.89</v>
@@ -18952,7 +18952,7 @@
         <v>58290689</v>
       </c>
       <c r="J343" t="n">
-        <v>0.00927591477247899</v>
+        <v>0.0092759147724789</v>
       </c>
       <c r="K343" t="n">
         <v>3.92</v>
@@ -19006,7 +19006,7 @@
         <v>43949443</v>
       </c>
       <c r="J344" t="n">
-        <v>0.006975407131288968</v>
+        <v>0.0069754071312889</v>
       </c>
       <c r="K344" t="n">
         <v>3.94</v>
@@ -19060,7 +19060,7 @@
         <v>132807140</v>
       </c>
       <c r="J345" t="n">
-        <v>0.02061867390622562</v>
+        <v>0.0206186739062256</v>
       </c>
       <c r="K345" t="n">
         <v>3.92</v>
@@ -19114,7 +19114,7 @@
         <v>96406563</v>
       </c>
       <c r="J346" t="n">
-        <v>0.01497864207274804</v>
+        <v>0.014978642072748</v>
       </c>
       <c r="K346" t="n">
         <v>4.03</v>
@@ -19168,7 +19168,7 @@
         <v>55331737</v>
       </c>
       <c r="J347" t="n">
-        <v>0.008595586517707088</v>
+        <v>0.008595586517706999</v>
       </c>
       <c r="K347" t="n">
         <v>3.99</v>
@@ -19222,7 +19222,7 @@
         <v>65346684</v>
       </c>
       <c r="J348" t="n">
-        <v>0.01021759797502998</v>
+        <v>0.0102175979750299</v>
       </c>
       <c r="K348" t="n">
         <v>4.02</v>
@@ -19276,7 +19276,7 @@
         <v>64618943</v>
       </c>
       <c r="J349" t="n">
-        <v>0.01018251279213844</v>
+        <v>0.0101825127921384</v>
       </c>
       <c r="K349" t="n">
         <v>3.96</v>
@@ -19330,7 +19330,7 @@
         <v>51680997</v>
       </c>
       <c r="J350" t="n">
-        <v>0.008120716721197086</v>
+        <v>0.008120716721197</v>
       </c>
       <c r="K350" t="n">
         <v>3.93</v>
@@ -19384,7 +19384,7 @@
         <v>46789375</v>
       </c>
       <c r="J351" t="n">
-        <v>0.007311617303004035</v>
+        <v>0.007311617303004</v>
       </c>
       <c r="K351" t="n">
         <v>3.97</v>
@@ -19438,7 +19438,7 @@
         <v>53140094</v>
       </c>
       <c r="J352" t="n">
-        <v>0.008352355342225384</v>
+        <v>0.008352355342225301</v>
       </c>
       <c r="K352" t="n">
         <v>3.97</v>
@@ -19456,7 +19456,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="n">
-        <v>0.9399871090528155</v>
+        <v>0.9399871090528156</v>
       </c>
     </row>
     <row r="353">
@@ -19492,7 +19492,7 @@
         <v>36978724</v>
       </c>
       <c r="J353" t="n">
-        <v>0.00582495854832412</v>
+        <v>0.0058249585483241</v>
       </c>
       <c r="K353" t="n">
         <v>3.93</v>
@@ -19546,7 +19546,7 @@
         <v>172671281</v>
       </c>
       <c r="J354" t="n">
-        <v>0.02652454923013641</v>
+        <v>0.0265245492301364</v>
       </c>
       <c r="K354" t="n">
         <v>4.1</v>
@@ -19564,7 +19564,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="n">
-        <v>3.332886271936511</v>
+        <v>3.332886271936512</v>
       </c>
     </row>
     <row r="355">
@@ -19600,7 +19600,7 @@
         <v>109158107</v>
       </c>
       <c r="J355" t="n">
-        <v>0.01676797646019123</v>
+        <v>0.0167679764601912</v>
       </c>
       <c r="K355" t="n">
         <v>4.02</v>
@@ -19654,7 +19654,7 @@
         <v>182545656</v>
       </c>
       <c r="J356" t="n">
-        <v>0.02750565581535108</v>
+        <v>0.027505655815351</v>
       </c>
       <c r="K356" t="n">
         <v>4.05</v>
@@ -19708,7 +19708,7 @@
         <v>272727382</v>
       </c>
       <c r="J357" t="n">
-        <v>0.04011489220435863</v>
+        <v>0.0401148922043586</v>
       </c>
       <c r="K357" t="n">
         <v>4.16</v>
@@ -19762,7 +19762,7 @@
         <v>161769736</v>
       </c>
       <c r="J358" t="n">
-        <v>0.02354123329787341</v>
+        <v>0.0235412332978734</v>
       </c>
       <c r="K358" t="n">
         <v>4.29</v>
@@ -19816,7 +19816,7 @@
         <v>248731055</v>
       </c>
       <c r="J359" t="n">
-        <v>0.03551433664814662</v>
+        <v>0.0355143366481466</v>
       </c>
       <c r="K359" t="n">
         <v>4.25</v>
@@ -19870,7 +19870,7 @@
         <v>145447912</v>
       </c>
       <c r="J360" t="n">
-        <v>0.02083509310608567</v>
+        <v>0.0208350931060856</v>
       </c>
       <c r="K360" t="n">
         <v>4.4</v>
@@ -19924,7 +19924,7 @@
         <v>155547202</v>
       </c>
       <c r="J361" t="n">
-        <v>0.02199025512477603</v>
+        <v>0.021990255124776</v>
       </c>
       <c r="K361" t="n">
         <v>4.34</v>
@@ -19978,7 +19978,7 @@
         <v>173201701</v>
       </c>
       <c r="J362" t="n">
-        <v>0.005579921829318194</v>
+        <v>0.0055799218293181</v>
       </c>
       <c r="K362" t="n">
         <v>23.05</v>
@@ -20032,7 +20032,7 @@
         <v>185849917</v>
       </c>
       <c r="J363" t="n">
-        <v>0.006089273545414105</v>
+        <v>0.0060892735454141</v>
       </c>
       <c r="K363" t="n">
         <v>23.19</v>
@@ -20047,10 +20047,10 @@
         <v>22.82</v>
       </c>
       <c r="O363" t="n">
-        <v>0.9890446976336547</v>
+        <v>0.9890446976336548</v>
       </c>
       <c r="P363" t="n">
-        <v>0.9065456702855123</v>
+        <v>0.9065456702855124</v>
       </c>
     </row>
     <row r="364">
@@ -20086,7 +20086,7 @@
         <v>185550780</v>
       </c>
       <c r="J364" t="n">
-        <v>0.005952531113065996</v>
+        <v>0.0059525311130659</v>
       </c>
       <c r="K364" t="n">
         <v>22.83</v>
@@ -20101,10 +20101,10 @@
         <v>22.96</v>
       </c>
       <c r="O364" t="n">
-        <v>0.9891114982578397</v>
+        <v>0.9891114982578396</v>
       </c>
       <c r="P364" t="n">
-        <v>0.9036742516117011</v>
+        <v>0.9036742516117012</v>
       </c>
     </row>
     <row r="365">
@@ -20140,7 +20140,7 @@
         <v>433485740</v>
       </c>
       <c r="J365" t="n">
-        <v>0.01479115582768678</v>
+        <v>0.0147911558276867</v>
       </c>
       <c r="K365" t="n">
         <v>22.96</v>
@@ -20155,7 +20155,7 @@
         <v>21.5</v>
       </c>
       <c r="O365" t="n">
-        <v>0.9893023255813953</v>
+        <v>0.9893023255813952</v>
       </c>
       <c r="P365" t="n">
         <v>2.299445225090793</v>
@@ -20194,7 +20194,7 @@
         <v>226759508</v>
       </c>
       <c r="J366" t="n">
-        <v>0.007793482389861443</v>
+        <v>0.0077934823898614</v>
       </c>
       <c r="K366" t="n">
         <v>21.67</v>
@@ -20248,7 +20248,7 @@
         <v>204499722</v>
       </c>
       <c r="J367" t="n">
-        <v>0.007108243803742404</v>
+        <v>0.0071082438037424</v>
       </c>
       <c r="K367" t="n">
         <v>21.7</v>
@@ -20263,7 +20263,7 @@
         <v>21.51</v>
       </c>
       <c r="O367" t="n">
-        <v>0.9893072989307299</v>
+        <v>0.98930729893073</v>
       </c>
       <c r="P367" t="n">
         <v>0.8839699704058511</v>
@@ -20302,7 +20302,7 @@
         <v>256686394</v>
       </c>
       <c r="J368" t="n">
-        <v>0.009167585565322846</v>
+        <v>0.0091675855653228</v>
       </c>
       <c r="K368" t="n">
         <v>21.25</v>
@@ -20317,10 +20317,10 @@
         <v>20.65</v>
       </c>
       <c r="O368" t="n">
-        <v>0.9893462469733657</v>
+        <v>0.9893462469733656</v>
       </c>
       <c r="P368" t="n">
-        <v>1.098317286489475</v>
+        <v>1.098317286489476</v>
       </c>
     </row>
     <row r="369">
@@ -20356,7 +20356,7 @@
         <v>202146615</v>
       </c>
       <c r="J369" t="n">
-        <v>0.007316834017944977</v>
+        <v>0.0073168340179449</v>
       </c>
       <c r="K369" t="n">
         <v>20.64</v>
@@ -20410,7 +20410,7 @@
         <v>317637513</v>
       </c>
       <c r="J370" t="n">
-        <v>0.01201625642857484</v>
+        <v>0.0120162564285748</v>
       </c>
       <c r="K370" t="n">
         <v>20.13</v>
@@ -20425,7 +20425,7 @@
         <v>19.5</v>
       </c>
       <c r="O370" t="n">
-        <v>0.9892307692307691</v>
+        <v>0.9892307692307692</v>
       </c>
       <c r="P370" t="n">
         <v>1.301099892267053</v>
@@ -20464,7 +20464,7 @@
         <v>192139942</v>
       </c>
       <c r="J371" t="n">
-        <v>0.007273096891295216</v>
+        <v>0.0072730968912952</v>
       </c>
       <c r="K371" t="n">
         <v>19.8</v>
@@ -20479,7 +20479,7 @@
         <v>19.89</v>
       </c>
       <c r="O371" t="n">
-        <v>0.9889391654097537</v>
+        <v>0.9889391654097536</v>
       </c>
       <c r="P371" t="n">
         <v>0.8378680121053904</v>
@@ -20518,7 +20518,7 @@
         <v>182772197</v>
       </c>
       <c r="J372" t="n">
-        <v>0.006687748172390216</v>
+        <v>0.0066877481723902</v>
       </c>
       <c r="K372" t="n">
         <v>20.11</v>
@@ -20533,7 +20533,7 @@
         <v>20.44</v>
       </c>
       <c r="O372" t="n">
-        <v>0.9892367906066535</v>
+        <v>0.9892367906066536</v>
       </c>
       <c r="P372" t="n">
         <v>0.7797847076671173</v>
@@ -20572,7 +20572,7 @@
         <v>142483153</v>
       </c>
       <c r="J373" t="n">
-        <v>0.005265719147131039</v>
+        <v>0.005265719147131</v>
       </c>
       <c r="K373" t="n">
         <v>20.58</v>
@@ -20587,7 +20587,7 @@
         <v>19.97</v>
       </c>
       <c r="O373" t="n">
-        <v>0.9889834752128193</v>
+        <v>0.9889834752128192</v>
       </c>
       <c r="P373" t="n">
         <v>0.6200577621518413</v>
@@ -20626,7 +20626,7 @@
         <v>273478503</v>
       </c>
       <c r="J374" t="n">
-        <v>0.009941438005754455</v>
+        <v>0.009941438005754401</v>
       </c>
       <c r="K374" t="n">
         <v>19.95</v>
@@ -20680,7 +20680,7 @@
         <v>346374694</v>
       </c>
       <c r="J375" t="n">
-        <v>0.01237321986244309</v>
+        <v>0.012373219862443</v>
       </c>
       <c r="K375" t="n">
         <v>20.05</v>
@@ -20734,7 +20734,7 @@
         <v>284055045</v>
       </c>
       <c r="J376" t="n">
-        <v>0.009947367806709184</v>
+        <v>0.009947367806709099</v>
       </c>
       <c r="K376" t="n">
         <v>21.22</v>
@@ -20788,7 +20788,7 @@
         <v>848954276</v>
       </c>
       <c r="J377" t="n">
-        <v>0.02777600454750443</v>
+        <v>0.0277760045475044</v>
       </c>
       <c r="K377" t="n">
         <v>23.03</v>
@@ -20842,7 +20842,7 @@
         <v>515576786</v>
       </c>
       <c r="J378" t="n">
-        <v>0.0168163334092568</v>
+        <v>0.0168163334092567</v>
       </c>
       <c r="K378" t="n">
         <v>22.53</v>
@@ -20896,7 +20896,7 @@
         <v>348106364</v>
       </c>
       <c r="J379" t="n">
-        <v>0.01134227447692278</v>
+        <v>0.0113422744769227</v>
       </c>
       <c r="K379" t="n">
         <v>22.93</v>
@@ -20950,7 +20950,7 @@
         <v>315316822</v>
       </c>
       <c r="J380" t="n">
-        <v>0.01003084935717883</v>
+        <v>0.0100308493571788</v>
       </c>
       <c r="K380" t="n">
         <v>22.93</v>
@@ -21004,7 +21004,7 @@
         <v>420628170</v>
       </c>
       <c r="J381" t="n">
-        <v>0.01332964995006859</v>
+        <v>0.0133296499500685</v>
       </c>
       <c r="K381" t="n">
         <v>23.55</v>
@@ -21019,7 +21019,7 @@
         <v>23.58</v>
       </c>
       <c r="O381" t="n">
-        <v>0.9889737065309585</v>
+        <v>0.9889737065309584</v>
       </c>
       <c r="P381" t="n">
         <v>0.8779576535831649</v>
@@ -21058,7 +21058,7 @@
         <v>282900566</v>
       </c>
       <c r="J382" t="n">
-        <v>0.008947230405410064</v>
+        <v>0.008947230405409999</v>
       </c>
       <c r="K382" t="n">
         <v>23.41</v>
@@ -21073,7 +21073,7 @@
         <v>23.66</v>
       </c>
       <c r="O382" t="n">
-        <v>0.9890109890109889</v>
+        <v>0.9890109890109888</v>
       </c>
       <c r="P382" t="n">
         <v>0.5641728858798987</v>
@@ -21112,7 +21112,7 @@
         <v>264447992</v>
       </c>
       <c r="J383" t="n">
-        <v>0.008398294510241032</v>
+        <v>0.008398294510240999</v>
       </c>
       <c r="K383" t="n">
         <v>23.66</v>
@@ -21166,7 +21166,7 @@
         <v>321711547</v>
       </c>
       <c r="J384" t="n">
-        <v>0.01030085355691042</v>
+        <v>0.0103008535569104</v>
       </c>
       <c r="K384" t="n">
         <v>23.19</v>
@@ -21184,7 +21184,7 @@
         <v>0.9891774891774892</v>
       </c>
       <c r="P384" t="n">
-        <v>0.9895475754470517</v>
+        <v>0.9895475754470516</v>
       </c>
     </row>
     <row r="385">
@@ -21220,7 +21220,7 @@
         <v>393057437</v>
       </c>
       <c r="J385" t="n">
-        <v>0.01289236886782381</v>
+        <v>0.0128923688678238</v>
       </c>
       <c r="K385" t="n">
         <v>23.06</v>
@@ -21274,7 +21274,7 @@
         <v>253847727</v>
       </c>
       <c r="J386" t="n">
-        <v>0.008288046869790707</v>
+        <v>0.0082880468697907</v>
       </c>
       <c r="K386" t="n">
         <v>22.7</v>
@@ -21289,7 +21289,7 @@
         <v>22.8</v>
       </c>
       <c r="O386" t="n">
-        <v>0.9890350877192983</v>
+        <v>0.9890350877192984</v>
       </c>
       <c r="P386" t="n">
         <v>0.7692865656557635</v>
@@ -21328,7 +21328,7 @@
         <v>209279010</v>
       </c>
       <c r="J387" t="n">
-        <v>0.006757403955173808</v>
+        <v>0.0067574039551738</v>
       </c>
       <c r="K387" t="n">
         <v>22.82</v>
@@ -21382,7 +21382,7 @@
         <v>175546862</v>
       </c>
       <c r="J388" t="n">
-        <v>0.005694680918383275</v>
+        <v>0.0056946809183832</v>
       </c>
       <c r="K388" t="n">
         <v>22.96</v>
@@ -21436,7 +21436,7 @@
         <v>197117561</v>
       </c>
       <c r="J389" t="n">
-        <v>0.006439528314325906</v>
+        <v>0.0064395283143259</v>
       </c>
       <c r="K389" t="n">
         <v>22.91</v>
@@ -21490,7 +21490,7 @@
         <v>174018591</v>
       </c>
       <c r="J390" t="n">
-        <v>0.005652472452085216</v>
+        <v>0.0056524724520852</v>
       </c>
       <c r="K390" t="n">
         <v>22.8</v>
@@ -21544,7 +21544,7 @@
         <v>130438191</v>
       </c>
       <c r="J391" t="n">
-        <v>0.004276494785748857</v>
+        <v>0.0042764947857488</v>
       </c>
       <c r="K391" t="n">
         <v>22.82</v>
@@ -21559,7 +21559,7 @@
         <v>22.74</v>
       </c>
       <c r="O391" t="n">
-        <v>0.9890061565523307</v>
+        <v>0.9890061565523308</v>
       </c>
       <c r="P391" t="n">
         <v>0.6512666797500476</v>
@@ -21598,7 +21598,7 @@
         <v>200096770</v>
       </c>
       <c r="J392" t="n">
-        <v>0.006503849810353212</v>
+        <v>0.0065038498103532</v>
       </c>
       <c r="K392" t="n">
         <v>22.65</v>
@@ -21652,7 +21652,7 @@
         <v>212042597</v>
       </c>
       <c r="J393" t="n">
-        <v>0.006833807159782837</v>
+        <v>0.0068338071597828</v>
       </c>
       <c r="K393" t="n">
         <v>22.88</v>
@@ -21706,7 +21706,7 @@
         <v>191498741</v>
       </c>
       <c r="J394" t="n">
-        <v>0.006272262611678766</v>
+        <v>0.0062722626116787</v>
       </c>
       <c r="K394" t="n">
         <v>23.11</v>
@@ -21760,7 +21760,7 @@
         <v>211848612</v>
       </c>
       <c r="J395" t="n">
-        <v>0.007030762114721422</v>
+        <v>0.0070307621147214</v>
       </c>
       <c r="K395" t="n">
         <v>22.6</v>
@@ -21814,7 +21814,7 @@
         <v>238297963</v>
       </c>
       <c r="J396" t="n">
-        <v>0.007865813141929415</v>
+        <v>0.0078658131419294</v>
       </c>
       <c r="K396" t="n">
         <v>22.76</v>
@@ -21868,7 +21868,7 @@
         <v>507951619</v>
       </c>
       <c r="J397" t="n">
-        <v>0.01751953729479927</v>
+        <v>0.0175195372947992</v>
       </c>
       <c r="K397" t="n">
         <v>22.62</v>
@@ -21883,7 +21883,7 @@
         <v>21.51</v>
       </c>
       <c r="O397" t="n">
-        <v>0.9893072989307299</v>
+        <v>0.98930729893073</v>
       </c>
       <c r="P397" t="n">
         <v>2.53858547163556</v>
@@ -21922,7 +21922,7 @@
         <v>541065520</v>
       </c>
       <c r="J398" t="n">
-        <v>0.01894941980329877</v>
+        <v>0.0189494198032987</v>
       </c>
       <c r="K398" t="n">
         <v>21.52</v>
@@ -21937,7 +21937,7 @@
         <v>21.41</v>
       </c>
       <c r="O398" t="n">
-        <v>0.9892573563755255</v>
+        <v>0.9892573563755256</v>
       </c>
       <c r="P398" t="n">
         <v>2.081339122637071</v>
@@ -21976,7 +21976,7 @@
         <v>354411199</v>
       </c>
       <c r="J399" t="n">
-        <v>0.01223888110129647</v>
+        <v>0.0122388811012964</v>
       </c>
       <c r="K399" t="n">
         <v>21.49</v>
@@ -21991,7 +21991,7 @@
         <v>21.49</v>
       </c>
       <c r="O399" t="n">
-        <v>0.9892973476035367</v>
+        <v>0.9892973476035368</v>
       </c>
       <c r="P399" t="n">
         <v>1.061706221449421</v>
@@ -22030,7 +22030,7 @@
         <v>368682336</v>
       </c>
       <c r="J400" t="n">
-        <v>0.01306563443191962</v>
+        <v>0.0130656344319196</v>
       </c>
       <c r="K400" t="n">
         <v>21.35</v>
@@ -22045,7 +22045,7 @@
         <v>20.96</v>
       </c>
       <c r="O400" t="n">
-        <v>0.9890267175572519</v>
+        <v>0.989026717557252</v>
       </c>
       <c r="P400" t="n">
         <v>1.027101243607002</v>
@@ -22084,7 +22084,7 @@
         <v>333093413</v>
       </c>
       <c r="J401" t="n">
-        <v>0.01194470901245501</v>
+        <v>0.011944709012455</v>
       </c>
       <c r="K401" t="n">
         <v>21</v>
@@ -22099,7 +22099,7 @@
         <v>20.69</v>
       </c>
       <c r="O401" t="n">
-        <v>0.9893668438859351</v>
+        <v>0.9893668438859352</v>
       </c>
       <c r="P401" t="n">
         <v>0.8576128315954347</v>
@@ -22138,7 +22138,7 @@
         <v>420839146</v>
       </c>
       <c r="J402" t="n">
-        <v>0.01479707743007307</v>
+        <v>0.014797077430073</v>
       </c>
       <c r="K402" t="n">
         <v>20.75</v>
@@ -22192,7 +22192,7 @@
         <v>275513477</v>
       </c>
       <c r="J403" t="n">
-        <v>0.009734752095402978</v>
+        <v>0.0097347520954029</v>
       </c>
       <c r="K403" t="n">
         <v>21.19</v>
@@ -22207,7 +22207,7 @@
         <v>21.12</v>
       </c>
       <c r="O403" t="n">
-        <v>0.9891098484848485</v>
+        <v>0.9891098484848484</v>
       </c>
       <c r="P403" t="n">
         <v>0.685587233389925</v>
@@ -22246,7 +22246,7 @@
         <v>229076744</v>
       </c>
       <c r="J404" t="n">
-        <v>0.008241689182538025</v>
+        <v>0.008241689182538</v>
       </c>
       <c r="K404" t="n">
         <v>21.3</v>
@@ -22300,7 +22300,7 @@
         <v>211390285</v>
       </c>
       <c r="J405" t="n">
-        <v>0.007816009819959072</v>
+        <v>0.007816009819959001</v>
       </c>
       <c r="K405" t="n">
         <v>20.61</v>
@@ -22315,7 +22315,7 @@
         <v>20</v>
       </c>
       <c r="O405" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.989</v>
       </c>
       <c r="P405" t="n">
         <v>0.6763142449137911</v>
@@ -22354,7 +22354,7 @@
         <v>297675742</v>
       </c>
       <c r="J406" t="n">
-        <v>0.01150421036476006</v>
+        <v>0.01150421036476</v>
       </c>
       <c r="K406" t="n">
         <v>19.88</v>
@@ -22369,7 +22369,7 @@
         <v>19.19</v>
       </c>
       <c r="O406" t="n">
-        <v>0.9890568004168837</v>
+        <v>0.9890568004168836</v>
       </c>
       <c r="P406" t="n">
         <v>1.094925033974929</v>
@@ -22408,7 +22408,7 @@
         <v>151935718</v>
       </c>
       <c r="J407" t="n">
-        <v>0.005948537664911716</v>
+        <v>0.0059485376649117</v>
       </c>
       <c r="K407" t="n">
         <v>19.3</v>
@@ -22423,7 +22423,7 @@
         <v>18.96</v>
       </c>
       <c r="O407" t="n">
-        <v>0.9889240506329113</v>
+        <v>0.9889240506329112</v>
       </c>
       <c r="P407" t="n">
         <v>0.5709455484814036</v>
@@ -22462,7 +22462,7 @@
         <v>148945137</v>
       </c>
       <c r="J408" t="n">
-        <v>0.005890495526984411</v>
+        <v>0.0058904955269844</v>
       </c>
       <c r="K408" t="n">
         <v>18.9</v>
@@ -22477,7 +22477,7 @@
         <v>18.96</v>
       </c>
       <c r="O408" t="n">
-        <v>0.9889240506329113</v>
+        <v>0.9889240506329112</v>
       </c>
       <c r="P408" t="n">
         <v>0.6810577411850564</v>
@@ -22516,7 +22516,7 @@
         <v>198022495</v>
       </c>
       <c r="J409" t="n">
-        <v>0.007789355528638926</v>
+        <v>0.0077893555286389</v>
       </c>
       <c r="K409" t="n">
         <v>19.06</v>
@@ -22570,7 +22570,7 @@
         <v>215493867</v>
       </c>
       <c r="J410" t="n">
-        <v>0.008567710473792445</v>
+        <v>0.0085677104737924</v>
       </c>
       <c r="K410" t="n">
         <v>18.63</v>
@@ -22624,7 +22624,7 @@
         <v>162102404</v>
       </c>
       <c r="J411" t="n">
-        <v>0.006522080445264312</v>
+        <v>0.0065220804452643</v>
       </c>
       <c r="K411" t="n">
         <v>18.64</v>
@@ -22732,7 +22732,7 @@
         <v>292506181</v>
       </c>
       <c r="J413" t="n">
-        <v>0.01153335031296608</v>
+        <v>0.011533350312966</v>
       </c>
       <c r="K413" t="n">
         <v>19.07</v>
@@ -22747,7 +22747,7 @@
         <v>18.96</v>
       </c>
       <c r="O413" t="n">
-        <v>0.9889240506329113</v>
+        <v>0.9889240506329112</v>
       </c>
       <c r="P413" t="n">
         <v>1.377603981475154</v>
@@ -22786,7 +22786,7 @@
         <v>219284212</v>
       </c>
       <c r="J414" t="n">
-        <v>0.008812735871463095</v>
+        <v>0.008812735871462999</v>
       </c>
       <c r="K414" t="n">
         <v>19</v>
@@ -22801,7 +22801,7 @@
         <v>18.51</v>
       </c>
       <c r="O414" t="n">
-        <v>0.9891950297136681</v>
+        <v>0.989195029713668</v>
       </c>
       <c r="P414" t="n">
         <v>0.9275971299218726</v>
@@ -22840,7 +22840,7 @@
         <v>197541524</v>
       </c>
       <c r="J415" t="n">
-        <v>0.007843650920789532</v>
+        <v>0.007843650920789501</v>
       </c>
       <c r="K415" t="n">
         <v>18.82</v>
@@ -22894,7 +22894,7 @@
         <v>257548649</v>
       </c>
       <c r="J416" t="n">
-        <v>0.01017542216771075</v>
+        <v>0.0101754221677107</v>
       </c>
       <c r="K416" t="n">
         <v>18.77</v>
@@ -22948,7 +22948,7 @@
         <v>286620597</v>
       </c>
       <c r="J417" t="n">
-        <v>0.01122143055942703</v>
+        <v>0.011221430559427</v>
       </c>
       <c r="K417" t="n">
         <v>18.85</v>
@@ -22966,7 +22966,7 @@
         <v>0.9889006342494714</v>
       </c>
       <c r="P417" t="n">
-        <v>1.090397273883513</v>
+        <v>1.090397273883514</v>
       </c>
     </row>
     <row r="418">
@@ -23002,7 +23002,7 @@
         <v>309393158</v>
       </c>
       <c r="J418" t="n">
-        <v>0.01207610597818078</v>
+        <v>0.0120761059781807</v>
       </c>
       <c r="K418" t="n">
         <v>18.87</v>
@@ -23056,7 +23056,7 @@
         <v>185294124</v>
       </c>
       <c r="J419" t="n">
-        <v>0.00731707326707852</v>
+        <v>0.0073170732670785</v>
       </c>
       <c r="K419" t="n">
         <v>18.91</v>
@@ -23071,7 +23071,7 @@
         <v>18.95</v>
       </c>
       <c r="O419" t="n">
-        <v>0.9889182058047493</v>
+        <v>0.9889182058047492</v>
       </c>
       <c r="P419" t="n">
         <v>0.7298193497691925</v>
@@ -23110,7 +23110,7 @@
         <v>383684646</v>
       </c>
       <c r="J420" t="n">
-        <v>0.01447492064585111</v>
+        <v>0.0144749206458511</v>
       </c>
       <c r="K420" t="n">
         <v>19</v>
@@ -23164,7 +23164,7 @@
         <v>452829128</v>
       </c>
       <c r="J421" t="n">
-        <v>0.01800242030535152</v>
+        <v>0.0180024203053515</v>
       </c>
       <c r="K421" t="n">
         <v>19.75</v>
@@ -23218,7 +23218,7 @@
         <v>407884808</v>
       </c>
       <c r="J422" t="n">
-        <v>0.01665773955604509</v>
+        <v>0.016657739556045</v>
       </c>
       <c r="K422" t="n">
         <v>19.32</v>
@@ -23272,7 +23272,7 @@
         <v>196275486</v>
       </c>
       <c r="J423" t="n">
-        <v>0.008005427309204446</v>
+        <v>0.008005427309204401</v>
       </c>
       <c r="K423" t="n">
         <v>18.14</v>
@@ -23287,7 +23287,7 @@
         <v>18.35</v>
       </c>
       <c r="O423" t="n">
-        <v>0.9891008174386919</v>
+        <v>0.989100817438692</v>
       </c>
       <c r="P423" t="n">
         <v>0.5840967900043292</v>
@@ -23326,7 +23326,7 @@
         <v>261392407</v>
       </c>
       <c r="J424" t="n">
-        <v>0.01054264946394044</v>
+        <v>0.0105426494639404</v>
       </c>
       <c r="K424" t="n">
         <v>18.13</v>
@@ -23341,7 +23341,7 @@
         <v>18.77</v>
       </c>
       <c r="O424" t="n">
-        <v>0.9893446989877465</v>
+        <v>0.9893446989877464</v>
       </c>
       <c r="P424" t="n">
         <v>0.8177974791109678</v>
@@ -23380,7 +23380,7 @@
         <v>262519743</v>
       </c>
       <c r="J425" t="n">
-        <v>0.01031784173604079</v>
+        <v>0.0103178417360407</v>
       </c>
       <c r="K425" t="n">
         <v>18.64</v>
@@ -23395,7 +23395,7 @@
         <v>19.03</v>
       </c>
       <c r="O425" t="n">
-        <v>0.9889647924330005</v>
+        <v>0.9889647924330004</v>
       </c>
       <c r="P425" t="n">
         <v>0.7622163438162923</v>
@@ -23434,7 +23434,7 @@
         <v>246647620</v>
       </c>
       <c r="J426" t="n">
-        <v>0.009677103488760753</v>
+        <v>0.0096771034887607</v>
       </c>
       <c r="K426" t="n">
         <v>19.15</v>
@@ -23488,7 +23488,7 @@
         <v>197962669</v>
       </c>
       <c r="J427" t="n">
-        <v>0.00770201021646122</v>
+        <v>0.0077020102164612</v>
       </c>
       <c r="K427" t="n">
         <v>19.15</v>
@@ -23542,7 +23542,7 @@
         <v>375284465</v>
       </c>
       <c r="J428" t="n">
-        <v>0.01471916792484444</v>
+        <v>0.0147191679248444</v>
       </c>
       <c r="K428" t="n">
         <v>19.05</v>
@@ -23596,7 +23596,7 @@
         <v>261346233</v>
       </c>
       <c r="J429" t="n">
-        <v>0.01038909027707479</v>
+        <v>0.0103890902770747</v>
       </c>
       <c r="K429" t="n">
         <v>18.86</v>
@@ -23650,7 +23650,7 @@
         <v>225639441</v>
       </c>
       <c r="J430" t="n">
-        <v>0.009043026205675344</v>
+        <v>0.009043026205675301</v>
       </c>
       <c r="K430" t="n">
         <v>18.45</v>
@@ -23704,7 +23704,7 @@
         <v>295155019</v>
       </c>
       <c r="J431" t="n">
-        <v>0.01225097175377103</v>
+        <v>0.012250971753771</v>
       </c>
       <c r="K431" t="n">
         <v>18.82</v>
@@ -23758,7 +23758,7 @@
         <v>199668979</v>
       </c>
       <c r="J432" t="n">
-        <v>0.008556326388852457</v>
+        <v>0.008556326388852399</v>
       </c>
       <c r="K432" t="n">
         <v>17.47</v>
@@ -23812,7 +23812,7 @@
         <v>241962022</v>
       </c>
       <c r="J433" t="n">
-        <v>0.01036085217139707</v>
+        <v>0.010360852171397</v>
       </c>
       <c r="K433" t="n">
         <v>17.4</v>
@@ -23830,7 +23830,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="n">
-        <v>0.9426054758535585</v>
+        <v>0.9426054758535584</v>
       </c>
     </row>
     <row r="434">
@@ -23866,7 +23866,7 @@
         <v>209332836</v>
       </c>
       <c r="J434" t="n">
-        <v>0.009098746658085558</v>
+        <v>0.009098746658085501</v>
       </c>
       <c r="K434" t="n">
         <v>17.12</v>
@@ -23920,7 +23920,7 @@
         <v>219771356</v>
       </c>
       <c r="J435" t="n">
-        <v>0.009690403057417894</v>
+        <v>0.0096904030574178</v>
       </c>
       <c r="K435" t="n">
         <v>16.98</v>
@@ -23938,7 +23938,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="n">
-        <v>0.9826017191793445</v>
+        <v>0.9826017191793444</v>
       </c>
     </row>
     <row r="436">
@@ -23974,7 +23974,7 @@
         <v>545169632</v>
       </c>
       <c r="J436" t="n">
-        <v>0.02568811537061879</v>
+        <v>0.0256881153706187</v>
       </c>
       <c r="K436" t="n">
         <v>16.66</v>
@@ -24028,7 +24028,7 @@
         <v>619389473</v>
       </c>
       <c r="J437" t="n">
-        <v>0.02858024684516683</v>
+        <v>0.0285802468451668</v>
       </c>
       <c r="K437" t="n">
         <v>15.44</v>
@@ -24082,7 +24082,7 @@
         <v>370138268</v>
       </c>
       <c r="J438" t="n">
-        <v>0.01665467627274645</v>
+        <v>0.0166546762727464</v>
       </c>
       <c r="K438" t="n">
         <v>16.83</v>
@@ -24136,7 +24136,7 @@
         <v>311811061</v>
       </c>
       <c r="J439" t="n">
-        <v>0.01314503309530656</v>
+        <v>0.0131450330953065</v>
       </c>
       <c r="K439" t="n">
         <v>16.48</v>
@@ -24190,7 +24190,7 @@
         <v>739426698</v>
       </c>
       <c r="J440" t="n">
-        <v>0.03059272186292696</v>
+        <v>0.0305927218629269</v>
       </c>
       <c r="K440" t="n">
         <v>17.65</v>
@@ -24244,7 +24244,7 @@
         <v>449180175</v>
       </c>
       <c r="J441" t="n">
-        <v>0.01902953472343753</v>
+        <v>0.0190295347234375</v>
       </c>
       <c r="K441" t="n">
         <v>18.12</v>
@@ -24298,7 +24298,7 @@
         <v>345139118</v>
       </c>
       <c r="J442" t="n">
-        <v>0.01465444917091004</v>
+        <v>0.01465444917091</v>
       </c>
       <c r="K442" t="n">
         <v>17.92</v>
@@ -24352,7 +24352,7 @@
         <v>225038485</v>
       </c>
       <c r="J443" t="n">
-        <v>0.009923507736577989</v>
+        <v>0.009923507736577899</v>
       </c>
       <c r="K443" t="n">
         <v>17.09</v>
@@ -24406,7 +24406,7 @@
         <v>277321970</v>
       </c>
       <c r="J444" t="n">
-        <v>0.01210031635078165</v>
+        <v>0.0121003163507816</v>
       </c>
       <c r="K444" t="n">
         <v>17.03</v>
@@ -24460,7 +24460,7 @@
         <v>765190896</v>
       </c>
       <c r="J445" t="n">
-        <v>0.03084076582443203</v>
+        <v>0.030840765824432</v>
       </c>
       <c r="K445" t="n">
         <v>17.75</v>
@@ -24514,7 +24514,7 @@
         <v>482851671</v>
       </c>
       <c r="J446" t="n">
-        <v>0.01929870565048594</v>
+        <v>0.0192987056504859</v>
       </c>
       <c r="K446" t="n">
         <v>18.5</v>
@@ -24568,7 +24568,7 @@
         <v>373648032</v>
       </c>
       <c r="J447" t="n">
-        <v>0.01436946246001807</v>
+        <v>0.014369462460018</v>
       </c>
       <c r="K447" t="n">
         <v>18.79</v>
@@ -24622,7 +24622,7 @@
         <v>252274493</v>
       </c>
       <c r="J448" t="n">
-        <v>0.009841412489498966</v>
+        <v>0.009841412489498901</v>
       </c>
       <c r="K448" t="n">
         <v>19.31</v>
@@ -24676,7 +24676,7 @@
         <v>549813239</v>
       </c>
       <c r="J449" t="n">
-        <v>0.02070496659266338</v>
+        <v>0.0207049665926633</v>
       </c>
       <c r="K449" t="n">
         <v>18.95</v>
@@ -24694,7 +24694,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="n">
-        <v>1.197501900390231</v>
+        <v>1.19750190039023</v>
       </c>
     </row>
     <row r="450">
@@ -24730,7 +24730,7 @@
         <v>714860882</v>
       </c>
       <c r="J450" t="n">
-        <v>0.02617212382102042</v>
+        <v>0.0261721238210204</v>
       </c>
       <c r="K450" t="n">
         <v>19.69</v>
@@ -24784,7 +24784,7 @@
         <v>491670172</v>
       </c>
       <c r="J451" t="n">
-        <v>0.01792867418224119</v>
+        <v>0.0179286741822411</v>
       </c>
       <c r="K451" t="n">
         <v>20.51</v>
@@ -24802,7 +24802,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="n">
-        <v>0.9917764412147861</v>
+        <v>0.991776441214786</v>
       </c>
     </row>
     <row r="452">
@@ -24838,7 +24838,7 @@
         <v>366555537</v>
       </c>
       <c r="J452" t="n">
-        <v>0.01317443390705382</v>
+        <v>0.0131744339070538</v>
       </c>
       <c r="K452" t="n">
         <v>20.54</v>
@@ -24946,7 +24946,7 @@
         <v>271583720</v>
       </c>
       <c r="J454" t="n">
-        <v>0.009527407318278754</v>
+        <v>0.0095274073182787</v>
       </c>
       <c r="K454" t="n">
         <v>21.38</v>
@@ -25000,7 +25000,7 @@
         <v>254734214</v>
       </c>
       <c r="J455" t="n">
-        <v>0.009158473229164911</v>
+        <v>0.009158473229164899</v>
       </c>
       <c r="K455" t="n">
         <v>20.92</v>
@@ -25054,7 +25054,7 @@
         <v>256091784</v>
       </c>
       <c r="J456" t="n">
-        <v>0.009056007520812166</v>
+        <v>0.0090560075208121</v>
       </c>
       <c r="K456" t="n">
         <v>20.84</v>
@@ -25108,7 +25108,7 @@
         <v>551014807</v>
       </c>
       <c r="J457" t="n">
-        <v>0.01845488513634565</v>
+        <v>0.0184548851363456</v>
       </c>
       <c r="K457" t="n">
         <v>21.26</v>
@@ -25162,7 +25162,7 @@
         <v>314817831</v>
       </c>
       <c r="J458" t="n">
-        <v>0.01042250987800605</v>
+        <v>0.010422509878006</v>
       </c>
       <c r="K458" t="n">
         <v>22.61</v>
@@ -25216,7 +25216,7 @@
         <v>301519512</v>
       </c>
       <c r="J459" t="n">
-        <v>0.01012785258297788</v>
+        <v>0.0101278525829778</v>
       </c>
       <c r="K459" t="n">
         <v>21.9</v>
@@ -25270,7 +25270,7 @@
         <v>678835270</v>
       </c>
       <c r="J460" t="n">
-        <v>0.02337843553901912</v>
+        <v>0.0233784355390191</v>
       </c>
       <c r="K460" t="n">
         <v>22.2</v>
@@ -25324,7 +25324,7 @@
         <v>350258216</v>
       </c>
       <c r="J461" t="n">
-        <v>0.01238894620735823</v>
+        <v>0.0123889462073582</v>
       </c>
       <c r="K461" t="n">
         <v>21.22</v>
@@ -25378,7 +25378,7 @@
         <v>303971260</v>
       </c>
       <c r="J462" t="n">
-        <v>0.01042918798466196</v>
+        <v>0.0104291879846619</v>
       </c>
       <c r="K462" t="n">
         <v>21.4</v>
@@ -25432,7 +25432,7 @@
         <v>542397305</v>
       </c>
       <c r="J463" t="n">
-        <v>0.01777214115100532</v>
+        <v>0.0177721411510053</v>
       </c>
       <c r="K463" t="n">
         <v>21.93</v>
@@ -25486,7 +25486,7 @@
         <v>336402761</v>
       </c>
       <c r="J464" t="n">
-        <v>0.01088417648408654</v>
+        <v>0.0108841764840865</v>
       </c>
       <c r="K464" t="n">
         <v>22.91</v>
@@ -25540,7 +25540,7 @@
         <v>430055151</v>
       </c>
       <c r="J465" t="n">
-        <v>0.01356345747014125</v>
+        <v>0.0135634574701412</v>
       </c>
       <c r="K465" t="n">
         <v>22.8</v>
@@ -25558,7 +25558,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="n">
-        <v>0.9060076335998717</v>
+        <v>0.9060076335998716</v>
       </c>
     </row>
     <row r="466">
@@ -25594,7 +25594,7 @@
         <v>356332289</v>
       </c>
       <c r="J466" t="n">
-        <v>0.01099282391304242</v>
+        <v>0.0109928239130424</v>
       </c>
       <c r="K466" t="n">
         <v>23.81</v>
@@ -25702,7 +25702,7 @@
         <v>269444127</v>
       </c>
       <c r="J468" t="n">
-        <v>0.008721869646802966</v>
+        <v>0.0087218696468029</v>
       </c>
       <c r="K468" t="n">
         <v>23.41</v>
@@ -25756,7 +25756,7 @@
         <v>169081167</v>
       </c>
       <c r="J469" t="n">
-        <v>0.00551535810285973</v>
+        <v>0.0055153581028597</v>
       </c>
       <c r="K469" t="n">
         <v>22.92</v>
@@ -25810,7 +25810,7 @@
         <v>174316168</v>
       </c>
       <c r="J470" t="n">
-        <v>0.005678717560307807</v>
+        <v>0.0056787175603078</v>
       </c>
       <c r="K470" t="n">
         <v>23.1</v>
@@ -25864,7 +25864,7 @@
         <v>158979880</v>
       </c>
       <c r="J471" t="n">
-        <v>0.005215521548551211</v>
+        <v>0.0052155215485512</v>
       </c>
       <c r="K471" t="n">
         <v>22.76</v>
@@ -25918,7 +25918,7 @@
         <v>199460425</v>
       </c>
       <c r="J472" t="n">
-        <v>0.006478980570979595</v>
+        <v>0.0064789805709795</v>
       </c>
       <c r="K472" t="n">
         <v>22.76</v>
@@ -25972,7 +25972,7 @@
         <v>280003976</v>
       </c>
       <c r="J473" t="n">
-        <v>0.009064582478075133</v>
+        <v>0.0090645824780751</v>
       </c>
       <c r="K473" t="n">
         <v>22.95</v>
@@ -25990,7 +25990,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="n">
-        <v>1.433795345398269</v>
+        <v>1.43379534539827</v>
       </c>
     </row>
     <row r="474">
@@ -26026,7 +26026,7 @@
         <v>224449129</v>
       </c>
       <c r="J474" t="n">
-        <v>0.00730665586788995</v>
+        <v>0.0073066558678899</v>
       </c>
       <c r="K474" t="n">
         <v>22.72</v>
@@ -26080,7 +26080,7 @@
         <v>305117293</v>
       </c>
       <c r="J475" t="n">
-        <v>0.009611964371862739</v>
+        <v>0.009611964371862699</v>
       </c>
       <c r="K475" t="n">
         <v>23</v>
@@ -26134,7 +26134,7 @@
         <v>159254942</v>
       </c>
       <c r="J476" t="n">
-        <v>0.00509852052368022</v>
+        <v>0.0050985205236802</v>
       </c>
       <c r="K476" t="n">
         <v>23.25</v>
@@ -26188,7 +26188,7 @@
         <v>224342247</v>
       </c>
       <c r="J477" t="n">
-        <v>0.006978366554475493</v>
+        <v>0.0069783665544754</v>
       </c>
       <c r="K477" t="n">
         <v>23.4</v>
@@ -26242,7 +26242,7 @@
         <v>109972224</v>
       </c>
       <c r="J478" t="n">
-        <v>0.003439851000290454</v>
+        <v>0.0034398510002904</v>
       </c>
       <c r="K478" t="n">
         <v>23.86</v>
@@ -26296,7 +26296,7 @@
         <v>144386613</v>
       </c>
       <c r="J479" t="n">
-        <v>0.004466803682980889</v>
+        <v>0.0044668036829808</v>
       </c>
       <c r="K479" t="n">
         <v>24.06</v>
@@ -26404,7 +26404,7 @@
         <v>303128374</v>
       </c>
       <c r="J481" t="n">
-        <v>0.009384530866089339</v>
+        <v>0.0093845308660893</v>
       </c>
       <c r="K481" t="n">
         <v>23.46</v>
@@ -26458,7 +26458,7 @@
         <v>160226800</v>
       </c>
       <c r="J482" t="n">
-        <v>0.01833429448610063</v>
+        <v>0.0183342944861006</v>
       </c>
       <c r="K482" t="n">
         <v>7.65</v>
@@ -26473,7 +26473,7 @@
         <v>7.63</v>
       </c>
       <c r="O482" t="n">
-        <v>0.9947575360419397</v>
+        <v>0.9947575360419396</v>
       </c>
       <c r="P482" t="n">
         <v>0.6468055306457423</v>
@@ -26512,7 +26512,7 @@
         <v>294060660</v>
       </c>
       <c r="J483" t="n">
-        <v>0.03314958146703517</v>
+        <v>0.0331495814670351</v>
       </c>
       <c r="K483" t="n">
         <v>7.61</v>
@@ -26566,7 +26566,7 @@
         <v>276390514</v>
       </c>
       <c r="J484" t="n">
-        <v>0.03129184003617935</v>
+        <v>0.0312918400361793</v>
       </c>
       <c r="K484" t="n">
         <v>7.72</v>
@@ -26620,7 +26620,7 @@
         <v>208632900</v>
       </c>
       <c r="J485" t="n">
-        <v>0.02360498445666557</v>
+        <v>0.0236049844566655</v>
       </c>
       <c r="K485" t="n">
         <v>7.65</v>
@@ -26635,10 +26635,10 @@
         <v>7.69</v>
       </c>
       <c r="O485" t="n">
-        <v>0.9947984395318595</v>
+        <v>0.9947984395318596</v>
       </c>
       <c r="P485" t="n">
-        <v>0.9052819319763099</v>
+        <v>0.90528193197631</v>
       </c>
     </row>
     <row r="486">
@@ -26674,7 +26674,7 @@
         <v>338227477</v>
       </c>
       <c r="J486" t="n">
-        <v>0.03829063782748608</v>
+        <v>0.038290637827486</v>
       </c>
       <c r="K486" t="n">
         <v>7.69</v>
@@ -26728,7 +26728,7 @@
         <v>271075640</v>
       </c>
       <c r="J487" t="n">
-        <v>0.03183976110706997</v>
+        <v>0.0318397611070699</v>
       </c>
       <c r="K487" t="n">
         <v>7.58</v>
@@ -26782,7 +26782,7 @@
         <v>201728922</v>
       </c>
       <c r="J488" t="n">
-        <v>0.02407425734328003</v>
+        <v>0.02407425734328</v>
       </c>
       <c r="K488" t="n">
         <v>7.35</v>
@@ -26836,7 +26836,7 @@
         <v>176930514</v>
       </c>
       <c r="J489" t="n">
-        <v>0.02151121158427175</v>
+        <v>0.0215112115842717</v>
       </c>
       <c r="K489" t="n">
         <v>7.23</v>
@@ -26905,7 +26905,7 @@
         <v>6.64</v>
       </c>
       <c r="O490" t="n">
-        <v>0.9939759036144579</v>
+        <v>0.993975903614458</v>
       </c>
       <c r="P490" t="n">
         <v>1.209591610408827</v>
@@ -26998,7 +26998,7 @@
         <v>138645089</v>
       </c>
       <c r="J492" t="n">
-        <v>0.01769200445672697</v>
+        <v>0.0176920044567269</v>
       </c>
       <c r="K492" t="n">
         <v>6.85</v>
@@ -27052,7 +27052,7 @@
         <v>112617927</v>
       </c>
       <c r="J493" t="n">
-        <v>0.01447342596013264</v>
+        <v>0.0144734259601326</v>
       </c>
       <c r="K493" t="n">
         <v>6.8</v>
@@ -27106,7 +27106,7 @@
         <v>124229222</v>
       </c>
       <c r="J494" t="n">
-        <v>0.01591568643552821</v>
+        <v>0.0159156864355282</v>
       </c>
       <c r="K494" t="n">
         <v>6.61</v>
@@ -27160,7 +27160,7 @@
         <v>98258153</v>
       </c>
       <c r="J495" t="n">
-        <v>0.0125500175181975</v>
+        <v>0.0125500175181974</v>
       </c>
       <c r="K495" t="n">
         <v>6.76</v>
@@ -27214,7 +27214,7 @@
         <v>114638185</v>
       </c>
       <c r="J496" t="n">
-        <v>0.01472306591134995</v>
+        <v>0.0147230659113499</v>
       </c>
       <c r="K496" t="n">
         <v>6.8</v>
@@ -27229,7 +27229,7 @@
         <v>6.68</v>
       </c>
       <c r="O496" t="n">
-        <v>0.9940119760479041</v>
+        <v>0.994011976047904</v>
       </c>
       <c r="P496" t="n">
         <v>0.9080982145502278</v>
@@ -27268,7 +27268,7 @@
         <v>75325308</v>
       </c>
       <c r="J497" t="n">
-        <v>0.009742082013719384</v>
+        <v>0.009742082013719299</v>
       </c>
       <c r="K497" t="n">
         <v>6.75</v>
@@ -27283,7 +27283,7 @@
         <v>6.72</v>
       </c>
       <c r="O497" t="n">
-        <v>0.9940476190476191</v>
+        <v>0.9940476190476192</v>
       </c>
       <c r="P497" t="n">
         <v>0.6464193088951714</v>
@@ -27322,7 +27322,7 @@
         <v>157829025</v>
       </c>
       <c r="J498" t="n">
-        <v>0.02028431954641188</v>
+        <v>0.0202843195464118</v>
       </c>
       <c r="K498" t="n">
         <v>6.71</v>
@@ -27340,7 +27340,7 @@
         <v>0.9940652818991098</v>
       </c>
       <c r="P498" t="n">
-        <v>1.504675978792044</v>
+        <v>1.504675978792045</v>
       </c>
     </row>
     <row r="499">
@@ -27376,7 +27376,7 @@
         <v>161105827</v>
       </c>
       <c r="J499" t="n">
-        <v>0.02157187815012029</v>
+        <v>0.0215718781501202</v>
       </c>
       <c r="K499" t="n">
         <v>6.74</v>
@@ -27430,7 +27430,7 @@
         <v>170943461</v>
       </c>
       <c r="J500" t="n">
-        <v>0.02258249028788199</v>
+        <v>0.0225824902878819</v>
       </c>
       <c r="K500" t="n">
         <v>6.44</v>
@@ -27484,7 +27484,7 @@
         <v>148698032</v>
       </c>
       <c r="J501" t="n">
-        <v>0.01932578676334046</v>
+        <v>0.0193257867633404</v>
       </c>
       <c r="K501" t="n">
         <v>6.68</v>
@@ -27499,7 +27499,7 @@
         <v>6.75</v>
       </c>
       <c r="O501" t="n">
-        <v>0.9940740740740741</v>
+        <v>0.994074074074074</v>
       </c>
       <c r="P501" t="n">
         <v>1.086892740095984</v>
@@ -27538,7 +27538,7 @@
         <v>116190603</v>
       </c>
       <c r="J502" t="n">
-        <v>0.01523975831116508</v>
+        <v>0.015239758311165</v>
       </c>
       <c r="K502" t="n">
         <v>6.68</v>
@@ -27592,7 +27592,7 @@
         <v>89904292</v>
       </c>
       <c r="J503" t="n">
-        <v>0.01175169795765577</v>
+        <v>0.0117516979576557</v>
       </c>
       <c r="K503" t="n">
         <v>6.63</v>
@@ -27607,7 +27607,7 @@
         <v>6.63</v>
       </c>
       <c r="O503" t="n">
-        <v>0.9939668174962293</v>
+        <v>0.9939668174962292</v>
       </c>
       <c r="P503" t="n">
         <v>0.5934947221227433</v>
@@ -27646,7 +27646,7 @@
         <v>150984884</v>
       </c>
       <c r="J504" t="n">
-        <v>0.01948834076770365</v>
+        <v>0.0194883407677036</v>
       </c>
       <c r="K504" t="n">
         <v>6.65</v>
@@ -27700,7 +27700,7 @@
         <v>220649435</v>
       </c>
       <c r="J505" t="n">
-        <v>0.02796925922988154</v>
+        <v>0.0279692592298815</v>
       </c>
       <c r="K505" t="n">
         <v>6.77</v>
@@ -27715,7 +27715,7 @@
         <v>6.89</v>
       </c>
       <c r="O505" t="n">
-        <v>0.9941944847605225</v>
+        <v>0.9941944847605224</v>
       </c>
       <c r="P505" t="n">
         <v>1.582185126135635</v>
@@ -27754,7 +27754,7 @@
         <v>175894604</v>
       </c>
       <c r="J506" t="n">
-        <v>0.02210226421055004</v>
+        <v>0.02210226421055</v>
       </c>
       <c r="K506" t="n">
         <v>6.9</v>
@@ -27808,7 +27808,7 @@
         <v>145201708</v>
       </c>
       <c r="J507" t="n">
-        <v>0.01835089631182165</v>
+        <v>0.0183508963118216</v>
       </c>
       <c r="K507" t="n">
         <v>6.93</v>
@@ -27823,7 +27823,7 @@
         <v>6.94</v>
       </c>
       <c r="O507" t="n">
-        <v>0.9942363112391931</v>
+        <v>0.9942363112391932</v>
       </c>
       <c r="P507" t="n">
         <v>0.9503182463569448</v>
@@ -27862,7 +27862,7 @@
         <v>113288064</v>
       </c>
       <c r="J508" t="n">
-        <v>0.01426248537123223</v>
+        <v>0.0142624853712322</v>
       </c>
       <c r="K508" t="n">
         <v>6.93</v>
@@ -27877,7 +27877,7 @@
         <v>6.92</v>
       </c>
       <c r="O508" t="n">
-        <v>0.9942196531791907</v>
+        <v>0.9942196531791908</v>
       </c>
       <c r="P508" t="n">
         <v>0.7155395115220863</v>
@@ -27970,7 +27970,7 @@
         <v>211039557</v>
       </c>
       <c r="J510" t="n">
-        <v>0.02615859497071102</v>
+        <v>0.026158594970711</v>
       </c>
       <c r="K510" t="n">
         <v>7.15</v>
@@ -28039,7 +28039,7 @@
         <v>6.94</v>
       </c>
       <c r="O511" t="n">
-        <v>0.9942363112391931</v>
+        <v>0.9942363112391932</v>
       </c>
       <c r="P511" t="n">
         <v>0.7906453570430977</v>
@@ -28078,7 +28078,7 @@
         <v>139514183</v>
       </c>
       <c r="J512" t="n">
-        <v>0.01778139208549531</v>
+        <v>0.0177813920854953</v>
       </c>
       <c r="K512" t="n">
         <v>6.9</v>
@@ -28093,7 +28093,7 @@
         <v>6.81</v>
       </c>
       <c r="O512" t="n">
-        <v>0.9941262848751835</v>
+        <v>0.9941262848751836</v>
       </c>
       <c r="P512" t="n">
         <v>0.791709511716307</v>
@@ -28132,7 +28132,7 @@
         <v>104234129</v>
       </c>
       <c r="J513" t="n">
-        <v>0.01351035237310361</v>
+        <v>0.0135103523731036</v>
       </c>
       <c r="K513" t="n">
         <v>6.78</v>
@@ -28186,7 +28186,7 @@
         <v>127693719</v>
       </c>
       <c r="J514" t="n">
-        <v>0.01685922917843953</v>
+        <v>0.0168592291784395</v>
       </c>
       <c r="K514" t="n">
         <v>6.69</v>
@@ -28294,7 +28294,7 @@
         <v>186739157</v>
       </c>
       <c r="J516" t="n">
-        <v>0.02534116597629257</v>
+        <v>0.0253411659762925</v>
       </c>
       <c r="K516" t="n">
         <v>6.25</v>
@@ -28348,7 +28348,7 @@
         <v>188098998</v>
       </c>
       <c r="J517" t="n">
-        <v>0.02481099192431397</v>
+        <v>0.0248109919243139</v>
       </c>
       <c r="K517" t="n">
         <v>6.38</v>
@@ -28402,7 +28402,7 @@
         <v>151894838</v>
       </c>
       <c r="J518" t="n">
-        <v>0.02007141874822552</v>
+        <v>0.0200714187482255</v>
       </c>
       <c r="K518" t="n">
         <v>6.58</v>
@@ -28456,7 +28456,7 @@
         <v>142432529</v>
       </c>
       <c r="J519" t="n">
-        <v>0.01891210961748908</v>
+        <v>0.018912109617489</v>
       </c>
       <c r="K519" t="n">
         <v>6.59</v>
@@ -28510,7 +28510,7 @@
         <v>83139849</v>
       </c>
       <c r="J520" t="n">
-        <v>0.01104805233496737</v>
+        <v>0.0110480523349673</v>
       </c>
       <c r="K520" t="n">
         <v>6.53</v>
@@ -28525,7 +28525,7 @@
         <v>6.55</v>
       </c>
       <c r="O520" t="n">
-        <v>0.9938931297709923</v>
+        <v>0.9938931297709924</v>
       </c>
       <c r="P520" t="n">
         <v>0.4326969684883904</v>
@@ -28564,7 +28564,7 @@
         <v>126986276</v>
       </c>
       <c r="J521" t="n">
-        <v>0.01686540001458705</v>
+        <v>0.016865400014587</v>
       </c>
       <c r="K521" t="n">
         <v>6.56</v>
@@ -28579,7 +28579,7 @@
         <v>6.55</v>
       </c>
       <c r="O521" t="n">
-        <v>0.9938931297709923</v>
+        <v>0.9938931297709924</v>
       </c>
       <c r="P521" t="n">
         <v>0.841723429872587</v>
@@ -28618,7 +28618,7 @@
         <v>157546228</v>
       </c>
       <c r="J522" t="n">
-        <v>0.02146987341184784</v>
+        <v>0.0214698734118478</v>
       </c>
       <c r="K522" t="n">
         <v>6.53</v>
@@ -28687,7 +28687,7 @@
         <v>6.48</v>
       </c>
       <c r="O523" t="n">
-        <v>0.9938271604938271</v>
+        <v>0.9938271604938272</v>
       </c>
       <c r="P523" t="n">
         <v>1.198651671667214</v>
@@ -28726,7 +28726,7 @@
         <v>119478394</v>
       </c>
       <c r="J524" t="n">
-        <v>0.01620300567561308</v>
+        <v>0.016203005675613</v>
       </c>
       <c r="K524" t="n">
         <v>6.48</v>
@@ -28741,7 +28741,7 @@
         <v>6.38</v>
       </c>
       <c r="O524" t="n">
-        <v>0.9937304075235109</v>
+        <v>0.9937304075235108</v>
       </c>
       <c r="P524" t="n">
         <v>0.9054017041517622</v>
@@ -28780,7 +28780,7 @@
         <v>123465850</v>
       </c>
       <c r="J525" t="n">
-        <v>0.01712341864405986</v>
+        <v>0.0171234186440598</v>
       </c>
       <c r="K525" t="n">
         <v>6.38</v>
@@ -28798,7 +28798,7 @@
         <v>0.9935897435897436</v>
       </c>
       <c r="P525" t="n">
-        <v>0.9867068522495799</v>
+        <v>0.98670685224958</v>
       </c>
     </row>
     <row r="526">
@@ -28834,7 +28834,7 @@
         <v>102536659</v>
       </c>
       <c r="J526" t="n">
-        <v>0.01452339913250504</v>
+        <v>0.014523399132505</v>
       </c>
       <c r="K526" t="n">
         <v>6.2</v>
@@ -28888,7 +28888,7 @@
         <v>92029571</v>
       </c>
       <c r="J527" t="n">
-        <v>0.01301141046774888</v>
+        <v>0.0130114104677488</v>
       </c>
       <c r="K527" t="n">
         <v>6.15</v>
@@ -28942,7 +28942,7 @@
         <v>77512269</v>
       </c>
       <c r="J528" t="n">
-        <v>0.01108932360308498</v>
+        <v>0.0110893236030849</v>
       </c>
       <c r="K528" t="n">
         <v>6.16</v>
@@ -28957,7 +28957,7 @@
         <v>6.07</v>
       </c>
       <c r="O528" t="n">
-        <v>0.9934102141680395</v>
+        <v>0.9934102141680397</v>
       </c>
       <c r="P528" t="n">
         <v>0.6758036968330215</v>
@@ -28996,7 +28996,7 @@
         <v>97075782</v>
       </c>
       <c r="J529" t="n">
-        <v>0.01401242661643522</v>
+        <v>0.0140124266164352</v>
       </c>
       <c r="K529" t="n">
         <v>6.09</v>
@@ -29014,7 +29014,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="n">
-        <v>0.9737538595134333</v>
+        <v>0.9737538595134332</v>
       </c>
     </row>
     <row r="530">
@@ -29050,7 +29050,7 @@
         <v>74717514</v>
       </c>
       <c r="J530" t="n">
-        <v>0.01094392838107061</v>
+        <v>0.0109439283810706</v>
       </c>
       <c r="K530" t="n">
         <v>5.95</v>
@@ -29104,7 +29104,7 @@
         <v>81011238</v>
       </c>
       <c r="J531" t="n">
-        <v>0.01193286091692906</v>
+        <v>0.011932860916929</v>
       </c>
       <c r="K531" t="n">
         <v>6.03</v>
@@ -29158,7 +29158,7 @@
         <v>109595355</v>
       </c>
       <c r="J532" t="n">
-        <v>0.01656502661478937</v>
+        <v>0.0165650266147893</v>
       </c>
       <c r="K532" t="n">
         <v>5.87</v>
@@ -29176,7 +29176,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="n">
-        <v>1.358012805289266</v>
+        <v>1.358012805289265</v>
       </c>
     </row>
     <row r="533">
@@ -29212,7 +29212,7 @@
         <v>111304179</v>
       </c>
       <c r="J533" t="n">
-        <v>0.01721716634827009</v>
+        <v>0.01721716634827</v>
       </c>
       <c r="K533" t="n">
         <v>5.74</v>
@@ -29266,7 +29266,7 @@
         <v>82997246</v>
       </c>
       <c r="J534" t="n">
-        <v>0.01303740583185219</v>
+        <v>0.0130374058318521</v>
       </c>
       <c r="K534" t="n">
         <v>5.57</v>
@@ -29320,7 +29320,7 @@
         <v>92207100</v>
       </c>
       <c r="J535" t="n">
-        <v>0.0142547010117496</v>
+        <v>0.0142547010117495</v>
       </c>
       <c r="K535" t="n">
         <v>5.55</v>
@@ -29374,7 +29374,7 @@
         <v>116557346</v>
       </c>
       <c r="J536" t="n">
-        <v>0.01814158054178859</v>
+        <v>0.0181415805417885</v>
       </c>
       <c r="K536" t="n">
         <v>5.55</v>
@@ -29482,7 +29482,7 @@
         <v>82116401</v>
       </c>
       <c r="J538" t="n">
-        <v>0.01323853755433899</v>
+        <v>0.0132385375543389</v>
       </c>
       <c r="K538" t="n">
         <v>5.43</v>
@@ -29536,7 +29536,7 @@
         <v>87660176</v>
       </c>
       <c r="J539" t="n">
-        <v>0.01438617753139179</v>
+        <v>0.0143861775313917</v>
       </c>
       <c r="K539" t="n">
         <v>5.37</v>
@@ -29554,7 +29554,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="n">
-        <v>0.9621874359769977</v>
+        <v>0.9621874359769976</v>
       </c>
     </row>
     <row r="540">
@@ -29590,7 +29590,7 @@
         <v>98729793</v>
       </c>
       <c r="J540" t="n">
-        <v>0.01641583522505766</v>
+        <v>0.0164158352250576</v>
       </c>
       <c r="K540" t="n">
         <v>5.24</v>
@@ -29644,7 +29644,7 @@
         <v>114303944</v>
       </c>
       <c r="J541" t="n">
-        <v>0.0193392579888588</v>
+        <v>0.0193392579888587</v>
       </c>
       <c r="K541" t="n">
         <v>5.09</v>
@@ -29698,7 +29698,7 @@
         <v>79187070</v>
       </c>
       <c r="J542" t="n">
-        <v>0.01360558413647181</v>
+        <v>0.0136055841364718</v>
       </c>
       <c r="K542" t="n">
         <v>5.1</v>
@@ -29752,7 +29752,7 @@
         <v>99536911</v>
       </c>
       <c r="J543" t="n">
-        <v>0.01701550286688124</v>
+        <v>0.0170155028668812</v>
       </c>
       <c r="K543" t="n">
         <v>5.07</v>
@@ -29806,7 +29806,7 @@
         <v>73943467</v>
       </c>
       <c r="J544" t="n">
-        <v>0.01269102225372166</v>
+        <v>0.0126910222537216</v>
       </c>
       <c r="K544" t="n">
         <v>5.07</v>
@@ -29860,7 +29860,7 @@
         <v>233910182</v>
       </c>
       <c r="J545" t="n">
-        <v>0.03910347649138251</v>
+        <v>0.0391034764913825</v>
       </c>
       <c r="K545" t="n">
         <v>5.12</v>
@@ -29914,7 +29914,7 @@
         <v>136487508</v>
       </c>
       <c r="J546" t="n">
-        <v>0.02281810466361446</v>
+        <v>0.0228181046636144</v>
       </c>
       <c r="K546" t="n">
         <v>5.24</v>
@@ -29968,7 +29968,7 @@
         <v>99719576</v>
       </c>
       <c r="J547" t="n">
-        <v>0.01665201785295015</v>
+        <v>0.0166520178529501</v>
       </c>
       <c r="K547" t="n">
         <v>5.21</v>
@@ -30022,7 +30022,7 @@
         <v>131078277</v>
       </c>
       <c r="J548" t="n">
-        <v>0.02240426590476344</v>
+        <v>0.0224042659047634</v>
       </c>
       <c r="K548" t="n">
         <v>5.25</v>
@@ -30076,7 +30076,7 @@
         <v>89711744</v>
       </c>
       <c r="J549" t="n">
-        <v>0.01561433727552303</v>
+        <v>0.015614337275523</v>
       </c>
       <c r="K549" t="n">
         <v>5.07</v>
@@ -30130,7 +30130,7 @@
         <v>100781753</v>
       </c>
       <c r="J550" t="n">
-        <v>0.01775946311299584</v>
+        <v>0.0177594631129958</v>
       </c>
       <c r="K550" t="n">
         <v>4.98</v>
@@ -30184,7 +30184,7 @@
         <v>125832217</v>
       </c>
       <c r="J551" t="n">
-        <v>0.02135218960594908</v>
+        <v>0.021352189605949</v>
       </c>
       <c r="K551" t="n">
         <v>5.03</v>
@@ -30202,7 +30202,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="n">
-        <v>1.120871161580641</v>
+        <v>1.120871161580642</v>
       </c>
     </row>
     <row r="552">
@@ -30238,7 +30238,7 @@
         <v>95129430</v>
       </c>
       <c r="J552" t="n">
-        <v>0.01681539816894053</v>
+        <v>0.0168153981689405</v>
       </c>
       <c r="K552" t="n">
         <v>5.07</v>
@@ -30292,7 +30292,7 @@
         <v>71432360</v>
       </c>
       <c r="J553" t="n">
-        <v>0.01276326065789922</v>
+        <v>0.0127632606578992</v>
       </c>
       <c r="K553" t="n">
         <v>4.87</v>
@@ -30346,7 +30346,7 @@
         <v>114471960</v>
       </c>
       <c r="J554" t="n">
-        <v>0.02054431836957382</v>
+        <v>0.0205443183695738</v>
       </c>
       <c r="K554" t="n">
         <v>4.84</v>
@@ -30400,7 +30400,7 @@
         <v>125735912</v>
       </c>
       <c r="J555" t="n">
-        <v>0.02262657327463849</v>
+        <v>0.0226265732746384</v>
       </c>
       <c r="K555" t="n">
         <v>4.77</v>
@@ -30454,7 +30454,7 @@
         <v>93288909</v>
       </c>
       <c r="J556" t="n">
-        <v>0.01702700953867815</v>
+        <v>0.0170270095386781</v>
       </c>
       <c r="K556" t="n">
         <v>4.81</v>
@@ -30472,7 +30472,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="n">
-        <v>0.9047127887723101</v>
+        <v>0.90471278877231</v>
       </c>
     </row>
     <row r="557">
@@ -30508,7 +30508,7 @@
         <v>192812067</v>
       </c>
       <c r="J557" t="n">
-        <v>0.03374269161795403</v>
+        <v>0.033742691617954</v>
       </c>
       <c r="K557" t="n">
         <v>4.75</v>
@@ -30562,7 +30562,7 @@
         <v>187516515</v>
       </c>
       <c r="J558" t="n">
-        <v>0.03199190149960155</v>
+        <v>0.0319919014996015</v>
       </c>
       <c r="K558" t="n">
         <v>5.05</v>
@@ -30616,7 +30616,7 @@
         <v>131320253</v>
       </c>
       <c r="J559" t="n">
-        <v>0.02265624490004004</v>
+        <v>0.02265624490004</v>
       </c>
       <c r="K559" t="n">
         <v>5.06</v>
@@ -30670,7 +30670,7 @@
         <v>139057920</v>
       </c>
       <c r="J560" t="n">
-        <v>0.02358289995337613</v>
+        <v>0.0235828999533761</v>
       </c>
       <c r="K560" t="n">
         <v>5.07</v>
@@ -30688,7 +30688,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="n">
-        <v>0.9208874467290645</v>
+        <v>0.9208874467290644</v>
       </c>
     </row>
     <row r="561">
@@ -30724,7 +30724,7 @@
         <v>124461825</v>
       </c>
       <c r="J561" t="n">
-        <v>0.02166788582966419</v>
+        <v>0.0216678858296641</v>
       </c>
       <c r="K561" t="n">
         <v>5.11</v>
@@ -30778,7 +30778,7 @@
         <v>89667888</v>
       </c>
       <c r="J562" t="n">
-        <v>0.01594312415220894</v>
+        <v>0.0159431241522089</v>
       </c>
       <c r="K562" t="n">
         <v>4.98</v>
@@ -30832,7 +30832,7 @@
         <v>89339749</v>
       </c>
       <c r="J563" t="n">
-        <v>0.01606434606635788</v>
+        <v>0.0160643460663578</v>
       </c>
       <c r="K563" t="n">
         <v>4.88</v>
@@ -30886,7 +30886,7 @@
         <v>128298297</v>
       </c>
       <c r="J564" t="n">
-        <v>0.02239148110005002</v>
+        <v>0.02239148110005</v>
       </c>
       <c r="K564" t="n">
         <v>4.86</v>
@@ -30940,7 +30940,7 @@
         <v>90529380</v>
       </c>
       <c r="J565" t="n">
-        <v>0.01606455286148645</v>
+        <v>0.0160645528614864</v>
       </c>
       <c r="K565" t="n">
         <v>4.99</v>
@@ -30994,7 +30994,7 @@
         <v>85287777</v>
       </c>
       <c r="J566" t="n">
-        <v>0.01517930114710639</v>
+        <v>0.0151793011471063</v>
       </c>
       <c r="K566" t="n">
         <v>4.84</v>
@@ -31048,7 +31048,7 @@
         <v>114202488</v>
       </c>
       <c r="J567" t="n">
-        <v>0.0197136770779913</v>
+        <v>0.0197136770779912</v>
       </c>
       <c r="K567" t="n">
         <v>4.9</v>
@@ -31102,7 +31102,7 @@
         <v>154165826</v>
       </c>
       <c r="J568" t="n">
-        <v>0.02627178749921658</v>
+        <v>0.0262717874992165</v>
       </c>
       <c r="K568" t="n">
         <v>5.01</v>
@@ -31156,7 +31156,7 @@
         <v>143777178</v>
       </c>
       <c r="J569" t="n">
-        <v>0.02494162649236126</v>
+        <v>0.0249416264923612</v>
       </c>
       <c r="K569" t="n">
         <v>5.09</v>
@@ -31210,7 +31210,7 @@
         <v>125237291</v>
       </c>
       <c r="J570" t="n">
-        <v>0.02194807585113593</v>
+        <v>0.0219480758511359</v>
       </c>
       <c r="K570" t="n">
         <v>4.93</v>
@@ -31318,7 +31318,7 @@
         <v>70847123</v>
       </c>
       <c r="J572" t="n">
-        <v>0.01256607715837135</v>
+        <v>0.0125660771583713</v>
       </c>
       <c r="K572" t="n">
         <v>4.87</v>
@@ -31372,7 +31372,7 @@
         <v>108987824</v>
       </c>
       <c r="J573" t="n">
-        <v>0.01907709563683071</v>
+        <v>0.0190770956368307</v>
       </c>
       <c r="K573" t="n">
         <v>4.93</v>
@@ -31426,7 +31426,7 @@
         <v>104516521</v>
       </c>
       <c r="J574" t="n">
-        <v>0.01844674150947882</v>
+        <v>0.0184467415094788</v>
       </c>
       <c r="K574" t="n">
         <v>4.97</v>
@@ -31444,7 +31444,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="n">
-        <v>0.9258318080879681</v>
+        <v>0.9258318080879679</v>
       </c>
     </row>
     <row r="575">
@@ -31480,7 +31480,7 @@
         <v>78822400</v>
       </c>
       <c r="J575" t="n">
-        <v>0.01389045398383634</v>
+        <v>0.0138904539838363</v>
       </c>
       <c r="K575" t="n">
         <v>4.86</v>
@@ -31534,7 +31534,7 @@
         <v>108793851</v>
       </c>
       <c r="J576" t="n">
-        <v>0.01880444668645505</v>
+        <v>0.018804446686455</v>
       </c>
       <c r="K576" t="n">
         <v>4.94</v>
@@ -31588,7 +31588,7 @@
         <v>102254152</v>
       </c>
       <c r="J577" t="n">
-        <v>0.01753733994718489</v>
+        <v>0.0175373399471848</v>
       </c>
       <c r="K577" t="n">
         <v>5.01</v>
@@ -31642,7 +31642,7 @@
         <v>166132703</v>
       </c>
       <c r="J578" t="n">
-        <v>0.02783904780984943</v>
+        <v>0.0278390478098494</v>
       </c>
       <c r="K578" t="n">
         <v>5.07</v>
@@ -31696,7 +31696,7 @@
         <v>140629024</v>
       </c>
       <c r="J579" t="n">
-        <v>0.02342215497194439</v>
+        <v>0.0234221549719443</v>
       </c>
       <c r="K579" t="n">
         <v>5.15</v>
@@ -31750,7 +31750,7 @@
         <v>115096284</v>
       </c>
       <c r="J580" t="n">
-        <v>0.01880352479724743</v>
+        <v>0.0188035247972474</v>
       </c>
       <c r="K580" t="n">
         <v>5.27</v>
@@ -31768,7 +31768,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="n">
-        <v>0.9263418486687517</v>
+        <v>0.9263418486687516</v>
       </c>
     </row>
     <row r="581">
@@ -31804,7 +31804,7 @@
         <v>109185278</v>
       </c>
       <c r="J581" t="n">
-        <v>0.01795755286176362</v>
+        <v>0.0179575528617636</v>
       </c>
       <c r="K581" t="n">
         <v>5.34</v>
@@ -31858,7 +31858,7 @@
         <v>142175559</v>
       </c>
       <c r="J582" t="n">
-        <v>0.02358295903769857</v>
+        <v>0.0235829590376985</v>
       </c>
       <c r="K582" t="n">
         <v>5.28</v>
@@ -31912,7 +31912,7 @@
         <v>181721476</v>
       </c>
       <c r="J583" t="n">
-        <v>0.0306089825372349</v>
+        <v>0.0306089825372348</v>
       </c>
       <c r="K583" t="n">
         <v>5.22</v>
@@ -31966,7 +31966,7 @@
         <v>119283839</v>
       </c>
       <c r="J584" t="n">
-        <v>0.02036619303958408</v>
+        <v>0.020366193039584</v>
       </c>
       <c r="K584" t="n">
         <v>5.16</v>
@@ -32020,7 +32020,7 @@
         <v>178080803</v>
       </c>
       <c r="J585" t="n">
-        <v>0.02938558516327045</v>
+        <v>0.0293855851632704</v>
       </c>
       <c r="K585" t="n">
         <v>5.2</v>
@@ -32074,7 +32074,7 @@
         <v>120278990</v>
       </c>
       <c r="J586" t="n">
-        <v>0.01991397901330254</v>
+        <v>0.0199139790133025</v>
       </c>
       <c r="K586" t="n">
         <v>5.31</v>
@@ -32128,7 +32128,7 @@
         <v>104097943</v>
       </c>
       <c r="J587" t="n">
-        <v>0.01725257871070722</v>
+        <v>0.0172525787107072</v>
       </c>
       <c r="K587" t="n">
         <v>5.19</v>
@@ -32182,7 +32182,7 @@
         <v>125223561</v>
       </c>
       <c r="J588" t="n">
-        <v>0.02079142638379678</v>
+        <v>0.0207914263837967</v>
       </c>
       <c r="K588" t="n">
         <v>5.26</v>
@@ -32290,7 +32290,7 @@
         <v>480537096</v>
       </c>
       <c r="J590" t="n">
-        <v>0.07658850653337537</v>
+        <v>0.0765885065333753</v>
       </c>
       <c r="K590" t="n">
         <v>5.4</v>
@@ -32470,7 +32470,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="n">
-        <v>1.890044240944807</v>
+        <v>1.890044240944806</v>
       </c>
     </row>
     <row r="594">
@@ -32560,7 +32560,7 @@
         <v>386339879</v>
       </c>
       <c r="J595" t="n">
-        <v>0.06351162976746608</v>
+        <v>0.06351162976746599</v>
       </c>
       <c r="K595" t="n">
         <v>5.4</v>
@@ -32614,7 +32614,7 @@
         <v>414588063</v>
       </c>
       <c r="J596" t="n">
-        <v>0.06661426223235131</v>
+        <v>0.0666142622323513</v>
       </c>
       <c r="K596" t="n">
         <v>5.25</v>
@@ -32668,7 +32668,7 @@
         <v>403201143</v>
       </c>
       <c r="J597" t="n">
-        <v>0.06315764082059445</v>
+        <v>0.0631576408205944</v>
       </c>
       <c r="K597" t="n">
         <v>5.39</v>
@@ -32722,7 +32722,7 @@
         <v>450240950</v>
       </c>
       <c r="J598" t="n">
-        <v>0.06895346790464923</v>
+        <v>0.06895346790464919</v>
       </c>
       <c r="K598" t="n">
         <v>5.52</v>
@@ -32776,7 +32776,7 @@
         <v>395176509</v>
       </c>
       <c r="J599" t="n">
-        <v>0.05902490621152327</v>
+        <v>0.0590249062115232</v>
       </c>
       <c r="K599" t="n">
         <v>5.85</v>
@@ -32830,7 +32830,7 @@
         <v>351718999</v>
       </c>
       <c r="J600" t="n">
-        <v>0.05304068442090487</v>
+        <v>0.0530406844209048</v>
       </c>
       <c r="K600" t="n">
         <v>5.88</v>
@@ -32982,16 +32982,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -33016,16 +33016,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -33050,16 +33050,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -33084,16 +33084,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -33118,16 +33118,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
